--- a/vulnerability-tests/vulnerability-test-report.xlsx
+++ b/vulnerability-tests/vulnerability-test-report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="1179">
   <si>
     <t>Test ID</t>
   </si>
@@ -292,3117 +292,3150 @@
     <t>SEC-VAL-232</t>
   </si>
   <si>
+    <t>Insecure handling of JWT tokens in local storage</t>
+  </si>
+  <si>
+    <t>Session token memory-only caching</t>
+  </si>
+  <si>
+    <t>Verify that the frontend stores session tokens in secure local state or ephemeral memories rather than persistent global cookies to prevent token leakage.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-233</t>
+  </si>
+  <si>
+    <t>Modifying token claims using custom browser setups</t>
+  </si>
+  <si>
+    <t>Cryptographic token integrity verification rules configuration</t>
+  </si>
+  <si>
+    <t>Verify that changing parameters inside token payloads causes decryption errors.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-234</t>
+  </si>
+  <si>
+    <t>Re-authenticating queries using old token storage caches</t>
+  </si>
+  <si>
+    <t>Strict non-cacheable headers parameters validation guidelines</t>
+  </si>
+  <si>
+    <t>Verify that auth endpoints send cache control headers to prevent reuse.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-235</t>
+  </si>
+  <si>
+    <t>Uploading script variables inside profile picture formats</t>
+  </si>
+  <si>
+    <t>File extension mime verification rules configurations checking</t>
+  </si>
+  <si>
+    <t>Verify that user images check for image mime profiles, blocking scripts.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-236</t>
+  </si>
+  <si>
+    <t>Bypassing size constraints using empty payload properties</t>
+  </si>
+  <si>
+    <t>Required parameters structure checking validators integration rules</t>
+  </si>
+  <si>
+    <t>Verify that schemas require non-empty variables to prevent null errors.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-237</t>
+  </si>
+  <si>
+    <t>Executing code inside user profile details addresses</t>
+  </si>
+  <si>
+    <t>Strict user profile inputs sanitization rules integrations checks</t>
+  </si>
+  <si>
+    <t>Verify that address fields strip custom formatting markup before storage.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-238</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document names description fields</t>
+  </si>
+  <si>
+    <t>Strict document metadata text validations parameters checks setup</t>
+  </si>
+  <si>
+    <t>Verify that document names strip tag characters to prevent stored XSS.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-239</t>
+  </si>
+  <si>
+    <t>Bypassing checks using hex-encoded string parameters queries</t>
+  </si>
+  <si>
+    <t>Strict decoding boundary constraint verification check rules guidelines</t>
+  </si>
+  <si>
+    <t>Verify that queries check parameters in original representations to prevent bypass.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-240</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member relationship titles</t>
+  </si>
+  <si>
+    <t>Family relationship text sanitization filter guidelines config rules</t>
+  </si>
+  <si>
+    <t>Verify that family notes strip script tags to block stored XSS.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-241</t>
+  </si>
+  <si>
+    <t>Bypassing checks using multi-byte Unicode parameters fields</t>
+  </si>
+  <si>
+    <t>Character normalization filters validation checking rules config</t>
+  </si>
+  <si>
+    <t>Verify that text parameters normalize Unicode strings to prevent character bypasses.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-242</t>
+  </si>
+  <si>
+    <t>Stored XSS inside notification message fields lists details</t>
+  </si>
+  <si>
+    <t>Notification templates text validation rules constraints integrations checking</t>
+  </si>
+  <si>
+    <t>Verify that notification fields strip tags to block scripting execution.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-243</t>
+  </si>
+  <si>
+    <t>SQL Injection via notification parameters search queries</t>
+  </si>
+  <si>
+    <t>Notification statements prepared query parameter bindings configuration</t>
+  </si>
+  <si>
+    <t>Verify that notification routes parameterize search fields.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-244</t>
+  </si>
+  <si>
+    <t>Executing commands in user profile details inputs</t>
+  </si>
+  <si>
+    <t>Strict profile details parameters sanitization validation rules checks</t>
+  </si>
+  <si>
+    <t>Verify that profile updates strip out shell control characters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-245</t>
+  </si>
+  <si>
+    <t>HTML Injection via document upload source metadata</t>
+  </si>
+  <si>
+    <t>Source tag parameters input sanitization filters rules checking</t>
+  </si>
+  <si>
+    <t>Verify that document source details discard formatting code.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-246</t>
+  </si>
+  <si>
+    <t>Bypassing checks using XML schema external descriptors</t>
+  </si>
+  <si>
+    <t>Parser disabled external references configurations checking rules</t>
+  </si>
+  <si>
+    <t>Verify that parsing uploads disables processing external schema definitions.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-247</t>
+  </si>
+  <si>
+    <t>Bypassing database constraints using long blood groups values</t>
+  </si>
+  <si>
+    <t>Blood groups category input restriction validations checks config</t>
+  </si>
+  <si>
+    <t>Verify that blood group parameters enforce strict length validations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-248</t>
+  </si>
+  <si>
+    <t>Injecting script arrays inside tag list parameters</t>
+  </si>
+  <si>
+    <t>String value array validation rules checking integrations setup</t>
+  </si>
+  <si>
+    <t>Verify that array values check that elements conform to string constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-249</t>
+  </si>
+  <si>
+    <t>Bypassing string filters using multiple slashes URL</t>
+  </si>
+  <si>
+    <t>Strict route normalization filters execution checks configuration</t>
+  </si>
+  <si>
+    <t>Verify that URL routes normalize double slashes to prevent route path bypassing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-250</t>
+  </si>
+  <si>
+    <t>Accessing folder directories via relative path downloads query</t>
+  </si>
+  <si>
+    <t>Path check resolve directory boundary constraint checks rules</t>
+  </si>
+  <si>
+    <t>Verify that file downloads block parameters seeking parent drive folders.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-251</t>
+  </si>
+  <si>
+    <t>Executing console actions via query string overrides</t>
+  </si>
+  <si>
+    <t>Endpoint parameters type verification checking guidelines config</t>
+  </si>
+  <si>
+    <t>Verify that API controller methods ignore parameters that do not match expected types.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-252</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member notes metadata</t>
+  </si>
+  <si>
+    <t>Strict notes field sanitization check validation guidelines rules</t>
+  </si>
+  <si>
+    <t>Verify that custom family member notes strip formatting tags before saving.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-253</t>
+  </si>
+  <si>
+    <t>Bypassing date structures using time parameters query</t>
+  </si>
+  <si>
+    <t>ISO-8601 strict date structure parsing validations checking checks</t>
+  </si>
+  <si>
+    <t>Verify that document expiry dates enforce standard date validations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-254</t>
+  </si>
+  <si>
+    <t>SQL Injection via document upload category values</t>
+  </si>
+  <si>
+    <t>Strict category code parameters verification constraints checking config</t>
+  </si>
+  <si>
+    <t>Verify that category inputs restrict values to allowed categories.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-255</t>
+  </si>
+  <si>
+    <t>Header Injection via custom logs formats parameters</t>
+  </si>
+  <si>
+    <t>Safe log formatter header sanitization integration rules checking</t>
+  </si>
+  <si>
+    <t>Verify that values logged from requests are sanitized to prevent log splitting.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-256</t>
+  </si>
+  <si>
+    <t>Executing system commands in custom parser config</t>
+  </si>
+  <si>
+    <t>Safe processor metadata validation checking rules guidelines setup</t>
+  </si>
+  <si>
+    <t>Verify that parser checks block system execution patterns in tags.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-257</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document descriptions text parameters</t>
+  </si>
+  <si>
+    <t>Description inputs sanitization rules setup configuration parameters</t>
+  </si>
+  <si>
+    <t>Verify that custom document description fields strip HTML tag entities.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-258</t>
+  </si>
+  <si>
+    <t>Bypassing blood type checks using special symbols text</t>
+  </si>
+  <si>
+    <t>Strict enum-based blood type checking configuration parameters guidelines</t>
+  </si>
+  <si>
+    <t>Verify that blood type updates reject fields that do not match expected patterns.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-259</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member email inputs parameter</t>
+  </si>
+  <si>
+    <t>Strict email input character validations configuration parameters checking</t>
+  </si>
+  <si>
+    <t>Verify that family email entries check for valid email structures, blocking scripts.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-260</t>
+  </si>
+  <si>
+    <t>Bypassing numeric limitations using float variables inputs</t>
+  </si>
+  <si>
+    <t>Strict integer type parameter validation configurations rules constraints</t>
+  </si>
+  <si>
+    <t>Verify that parameters requiring integer formats reject float values.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-261</t>
+  </si>
+  <si>
+    <t>Stored XSS inside user organization name field</t>
+  </si>
+  <si>
+    <t>HTML tags stripping on organization details</t>
+  </si>
+  <si>
+    <t>Verify that updating the user's organization name strips script tags to prevent stored script execution.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-262</t>
+  </si>
+  <si>
+    <t>SQL Injection via document tag delete route queries</t>
+  </si>
+  <si>
+    <t>Strict tag parameter binding configurations validation checks rules</t>
+  </si>
+  <si>
+    <t>Verify that deleting tag items parameterizes values safely.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-263</t>
+  </si>
+  <si>
+    <t>Bypassing size constraints using null request parameter keys</t>
+  </si>
+  <si>
+    <t>Schema keys existence check validation rules checking integrations</t>
+  </si>
+  <si>
+    <t>Verify that requests require required schema properties, blocking null formats.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-264</t>
+  </si>
+  <si>
+    <t>Executing commands in user profile metadata details parsing</t>
+  </si>
+  <si>
+    <t>Strict user profile parser validations checking rules parameters checking</t>
+  </si>
+  <si>
+    <t>Verify that profile updates strip system indicators from string variables.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-265</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document custom category selections</t>
+  </si>
+  <si>
+    <t>Strict category text inputs validations parameters checking integration</t>
+  </si>
+  <si>
+    <t>Verify that document category parameters strip tag elements.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-266</t>
+  </si>
+  <si>
+    <t>Bypassing type constraints using hex-encoded request string params</t>
+  </si>
+  <si>
+    <t>Strict input decoding boundary constraints checking parameters validation</t>
+  </si>
+  <si>
+    <t>Verify that hex-encoded inputs are rejected unless allowed by schema rules.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-267</t>
+  </si>
+  <si>
+    <t>Stored XSS inside custom document tags descriptions</t>
+  </si>
+  <si>
+    <t>Strictly encoded rendering of tag labels</t>
+  </si>
+  <si>
+    <t>Verify that document tag strings escape tag characters before output rendering to block markup injections.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-268</t>
+  </si>
+  <si>
+    <t>Bypassing size validation using array representation query params</t>
+  </si>
+  <si>
+    <t>Strict parameter structure check validation configurations rules parameters</t>
+  </si>
+  <si>
+    <t>Verify that endpoints validate parameter structure matches expected string constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-269</t>
+  </si>
+  <si>
+    <t>SQL Injection via document category filter inputs variables</t>
+  </si>
+  <si>
+    <t>Strict input parameter enumerations validation checks rules configuration</t>
+  </si>
+  <si>
+    <t>Verify that category filters match approved enumerations list to prevent SQL injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-270</t>
+  </si>
+  <si>
+    <t>SQL Injection via tags update array parameters queries</t>
+  </si>
+  <si>
+    <t>Safe array input ORM query constraints validation checks parameters</t>
+  </si>
+  <si>
+    <t>Verify that array values inside update queries are parsed as data variables.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-271</t>
+  </si>
+  <si>
+    <t>SQL Injection via document ID route parameters queries</t>
+  </si>
+  <si>
+    <t>UUID pattern route validation constraints checking parameters config</t>
+  </si>
+  <si>
+    <t>Verify that route routes check for UUID formats, blocking injection strings.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-272</t>
+  </si>
+  <si>
+    <t>SQL Injection via notifications filter queries parameters checking</t>
+  </si>
+  <si>
+    <t>Database prepared statements setup verification checks guidelines rules</t>
+  </si>
+  <si>
+    <t>Verify that alert filters parameterize options to prevent SQL injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-273</t>
+  </si>
+  <si>
+    <t>NoSQL Injection via custom JSON parameters query options</t>
+  </si>
+  <si>
+    <t>JSON schema validator parameters filters check parameters rules constraints</t>
+  </si>
+  <si>
+    <t>Verify that endpoints reject objects containing NoSQL operators.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-274</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document names metadata parameter details</t>
+  </si>
+  <si>
+    <t>HTML entities output escaping and sanitization parameters checking rules</t>
+  </si>
+  <si>
+    <t>Verify that custom document names strip out HTML tag symbols before database writes.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-275</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member details addresses attributes parameters</t>
+  </si>
+  <si>
+    <t>Strict HTML tags inputs sanitization filters rules constraints checking</t>
+  </si>
+  <si>
+    <t>Verify that family addresses are sanitized to prevent stored script injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-276</t>
+  </si>
+  <si>
+    <t>Reflected XSS via categories search filter inputs variables</t>
+  </si>
+  <si>
+    <t>Sanitized HTTP request parameters rendering rules checking guidelines config</t>
+  </si>
+  <si>
+    <t>Verify that search values are encoded before rendering in application logs.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-277</t>
+  </si>
+  <si>
+    <t>Reflected XSS via notification ID route queries options</t>
+  </si>
+  <si>
+    <t>HTML entity output encoding filters integration parameters check rules</t>
+  </si>
+  <si>
+    <t>Verify that notification lookups validate inputs before processing search variables.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-278</t>
+  </si>
+  <si>
+    <t>HTML Injection inside profile names updates parameter variables</t>
+  </si>
+  <si>
+    <t>HTML tags removal regex filters check parameters validation rules</t>
+  </si>
+  <si>
+    <t>Verify that profile names discard tag parameters to block rendering manipulation.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-279</t>
+  </si>
+  <si>
+    <t>System command injection via image metadata parameters</t>
+  </si>
+  <si>
+    <t>EXIF parser parameter filtering</t>
+  </si>
+  <si>
+    <t>Verify that processing image EXIF tags strips shell execution characters before parsing metadata.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-280</t>
+  </si>
+  <si>
+    <t>Directory traversal via profile avatar upload paths</t>
+  </si>
+  <si>
+    <t>Avatar destination folder isolation</t>
+  </si>
+  <si>
+    <t>Verify that profile avatar uploads are forced into the isolated avatar subdirectory, ignoring custom path parameters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-281</t>
+  </si>
+  <si>
+    <t>Directory traversal using boundary path strings details</t>
+  </si>
+  <si>
+    <t>Strict path directories boundary resolve limits checking rules parameters</t>
+  </si>
+  <si>
+    <t>Verify that relative path indicators are stripped from file search queries.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-282</t>
+  </si>
+  <si>
+    <t>Buffer overflow via large text fields payloads variables</t>
+  </si>
+  <si>
+    <t>Schema character limit size constraints rules checking configurations</t>
+  </si>
+  <si>
+    <t>Verify that database fields reject strings exceeding column width declarations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-283</t>
+  </si>
+  <si>
+    <t>Integer overflow via bulk download file count query</t>
+  </si>
+  <si>
+    <t>Max batch size limit check</t>
+  </si>
+  <si>
+    <t>Verify that bulk downloads validate that the file count parameter does not exceed 100, blocking memory allocation exploits.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-284</t>
+  </si>
+  <si>
+    <t>Invalid email syntax during user invitation requests details</t>
+  </si>
+  <si>
+    <t>Strict email format constraint regex rules constraints checking parameters</t>
+  </si>
+  <si>
+    <t>Verify that invites block emails lacking proper domain and suffix formats.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-285</t>
+  </si>
+  <si>
+    <t>Invalid mobile formatting inputs during registration options</t>
+  </si>
+  <si>
+    <t>Strict digits validation filter rules configuration parameters checking rules</t>
+  </si>
+  <si>
+    <t>Verify that mobile inputs reject letters and enforce 10-digit constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-286</t>
+  </si>
+  <si>
+    <t>Application crash via malformed JSON payload bodies variables</t>
+  </si>
+  <si>
+    <t>Global custom JSON parsing middleware wrappers checking rules parameters</t>
+  </si>
+  <si>
+    <t>Verify that invalid JSON formatting returns a 400 instead of crashing processes.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-287</t>
+  </si>
+  <si>
+    <t>Unrestricted file size memory exhaustion checks options</t>
+  </si>
+  <si>
+    <t>Upload parser payload size limits configuration parameters rules checking</t>
+  </si>
+  <si>
+    <t>Verify that uploads reject files larger than 10MB to prevent resource starvation.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-288</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document tags lists parameter details</t>
+  </si>
+  <si>
+    <t>String array element sanitization filters config rules checking integrations</t>
+  </si>
+  <si>
+    <t>Verify that array fields sanitize each element before database insertion.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-289</t>
+  </si>
+  <si>
+    <t>SQL Injection via custom document sorting parameter queries</t>
+  </si>
+  <si>
+    <t>Sort parameters whitelist checking verification parameters checking guidelines</t>
+  </si>
+  <si>
+    <t>Verify that order-by inputs validate against allowed column keys list.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-290</t>
+  </si>
+  <si>
+    <t>SQL Injection via profile details address attributes queries</t>
+  </si>
+  <si>
+    <t>Database statement query parameters execution checks rules validation checking</t>
+  </si>
+  <si>
+    <t>Verify that profile updates parameterize address values safely.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-291</t>
+  </si>
+  <si>
+    <t>XML External Entity injection via upload streams details</t>
+  </si>
+  <si>
+    <t>External entity parsing restrictions validation rules constraints checking parameter</t>
+  </si>
+  <si>
+    <t>Verify that XML parsers reject external entity references to prevent file reading.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-292</t>
+  </si>
+  <si>
+    <t>System configuration reading via environment paths traversal variables</t>
+  </si>
+  <si>
+    <t>Path check resolve sandbox boundary verification rules checking parameters</t>
+  </si>
+  <si>
+    <t>Verify that path parameters block attempts to access system config directories.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-293</t>
+  </si>
+  <si>
+    <t>Input parameter bypass using HTTP Parameter Pollution options</t>
+  </si>
+  <si>
+    <t>Strict query parameter object parsing validators parameters rules constraints</t>
+  </si>
+  <si>
+    <t>Verify that duplicate query parameters are processed as a single string.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-294</t>
+  </si>
+  <si>
+    <t>Bypassing filters using URL double-encoding variables details</t>
+  </si>
+  <si>
+    <t>Safe route parameter decoding filters configurations parameters checking rules</t>
+  </si>
+  <si>
+    <t>Verify that route parameters decode safely to prevent filters bypass.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-295</t>
+  </si>
+  <si>
+    <t>Zip Slip vulnerability when unpacking compressed assets</t>
+  </si>
+  <si>
+    <t>Canonical path validation checks on zip entries</t>
+  </si>
+  <si>
+    <t>Verify that extracting zip archives checks the canonical path of entries to prevent files from writing outside the target folder.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-296</t>
+  </si>
+  <si>
+    <t>Bypassing string checks using multi-byte Unicode strings variables</t>
+  </si>
+  <si>
+    <t>UTF-8 string normalization parameter checks rules checking configurations parameters</t>
+  </si>
+  <si>
+    <t>Verify that text parser normalizes string symbols to prevent character bypasses.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-297</t>
+  </si>
+  <si>
+    <t>Submitting negative values to array index lookups details</t>
+  </si>
+  <si>
+    <t>Index lookup unsigned boundary verification rules constraints checking parameters</t>
+  </si>
+  <si>
+    <t>Verify that database offsets require positive integer formats.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-298</t>
+  </si>
+  <si>
+    <t>Application crash via nested JSON object array depth variables</t>
+  </si>
+  <si>
+    <t>Max JSON parsing depth configuration rules checking configurations parameters validation</t>
+  </si>
+  <si>
+    <t>Verify that JSON parser rejects objects exceeding 20 levels of nesting depth.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-299</t>
+  </si>
+  <si>
+    <t>Uploading malicious PHP scripts as document content</t>
+  </si>
+  <si>
+    <t>File parser MIME-type check</t>
+  </si>
+  <si>
+    <t>Verify that the document processing engine blocks documents containing PHP tags or server-side scripts from executing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-300</t>
+  </si>
+  <si>
+    <t>Bypassing date structures using invalid date formats options</t>
+  </si>
+  <si>
+    <t>Strict ISO-8601 date validator validations parameters checking rules constraints</t>
+  </si>
+  <si>
+    <t>Verify that date-based query filters reject malformed date representations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-301</t>
+  </si>
+  <si>
+    <t>SQL Injection via family member blood group values</t>
+  </si>
+  <si>
+    <t>Enforced array inclusion checks on blood groups</t>
+  </si>
+  <si>
+    <t>Verify that the blood group parameter checks input values against a strict list of valid blood types to prevent database injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-302</t>
+  </si>
+  <si>
+    <t>Header Injection via user agent logging parameter</t>
+  </si>
+  <si>
+    <t>Line break removal in system logs</t>
+  </si>
+  <si>
+    <t>Verify that logging request user agents strips out carriage return and line feed (CRLF) characters to block log manipulation.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-303</t>
+  </si>
+  <si>
+    <t>Executing local server commands via search query parameters</t>
+  </si>
+  <si>
+    <t>Argument parameter binding on system tools</t>
+  </si>
+  <si>
+    <t>Verify that querying search indexes binds query arguments safely to prevent local command executions.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-304</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document category text fields options</t>
+  </si>
+  <si>
+    <t>Strict category parameter sanitization filters config rules checking parameters checking</t>
+  </si>
+  <si>
+    <t>Verify that category inputs block custom script injections.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-305</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member relationship descriptions variables</t>
+  </si>
+  <si>
+    <t>Family member description sanitization filters config rules checking configurations limits</t>
+  </si>
+  <si>
+    <t>Verify that relationship parameters strip out script tags before storage.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-001</t>
+  </si>
+  <si>
+    <t>Authentication</t>
+  </si>
+  <si>
+    <t>Brute-force password guessing attacks on login form</t>
+  </si>
+  <si>
+    <t>Express Rate Limit middleware on auth routes</t>
+  </si>
+  <si>
+    <t>Verify that successive failed login attempts from a single IP address trigger a temporary lockout to prevent credential brute forcing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-002</t>
+  </si>
+  <si>
+    <t>Storage of plain-text passwords in database</t>
+  </si>
+  <si>
+    <t>Bcrypt cryptographic hashing with salt rounds</t>
+  </si>
+  <si>
+    <t>Verify that user passwords are encrypted using bcrypt before being written to the users database table.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-003</t>
+  </si>
+  <si>
+    <t>Setting weak or short passwords during registration</t>
+  </si>
+  <si>
+    <t>Backend password length threshold checker</t>
+  </si>
+  <si>
+    <t>Verify that the signup API rejects password entries shorter than 6 characters with a validation error.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-004</t>
+  </si>
+  <si>
+    <t>Registering multiple accounts with the same email</t>
+  </si>
+  <si>
+    <t>Unique database index on email column</t>
+  </si>
+  <si>
+    <t>Verify that the registration service blocks duplicate signups for the same email address, returning a 409 status.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-005</t>
+  </si>
+  <si>
+    <t>Accessing secure endpoints using an expired JWT token</t>
+  </si>
+  <si>
+    <t>Token expiration timestamp validation</t>
+  </si>
+  <si>
+    <t>Verify that the gateway rejects tokens that have passed their exp timestamp and returns a 401 response.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-006</t>
+  </si>
+  <si>
+    <t>Bypassing signatures by stripping cryptographic hashes</t>
+  </si>
+  <si>
+    <t>Strict JWT signature verification rules</t>
+  </si>
+  <si>
+    <t>Verify that the server blocks tokens whose signature portion has been altered or omitted completely.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-007</t>
+  </si>
+  <si>
+    <t>Bypassing signatures by changing algorithm to none</t>
+  </si>
+  <si>
+    <t>Algorithm whitelist constraint validation</t>
+  </si>
+  <si>
+    <t>Verify that JWT libraries explicitly reject tokens specifying "none" in the header algorithm parameters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-008</t>
+  </si>
+  <si>
+    <t>Replaying session tokens after a logout request</t>
+  </si>
+  <si>
+    <t>Server-side token validation lookup</t>
+  </si>
+  <si>
+    <t>Verify that calling logout invalidates the active session identifier so the token cannot be reused.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-009</t>
+  </si>
+  <si>
+    <t>Intercepting session cookies over unencrypted HTTP</t>
+  </si>
+  <si>
+    <t>Secure flag cookie attributes configuration</t>
+  </si>
+  <si>
+    <t>Verify that the server only transmits authentication cookies over encrypted HTTPS channels.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-010</t>
+  </si>
+  <si>
+    <t>Reading session cookies using malicious browser scripts</t>
+  </si>
+  <si>
+    <t>HttpOnly flag cookie attributes configuration</t>
+  </si>
+  <si>
+    <t>Verify that cookies are set with the HttpOnly flag to prevent XSS scripts from reading session identifiers.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-011</t>
+  </si>
+  <si>
+    <t>Cross-Site Request Forgery cookie submissions</t>
+  </si>
+  <si>
+    <t>SameSite=Lax cookie attribute enforcement</t>
+  </si>
+  <si>
+    <t>Verify that authentication cookies enforce SameSite attributes to block cross-site script request forgeries.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-012</t>
+  </si>
+  <si>
+    <t>Accessing resources without any authorization header</t>
+  </si>
+  <si>
+    <t>Authentication check gateway middleware</t>
+  </si>
+  <si>
+    <t>Verify that requesting protected backend resources without a token returns a 401 unauthorized status.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-013</t>
+  </si>
+  <si>
+    <t>Modifying claims inside the token to escalate roles</t>
+  </si>
+  <si>
+    <t>Token payload integrity validations</t>
+  </si>
+  <si>
+    <t>Verify that changes to the payload parameters of a JWT are detected and rejected by signature verification.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-014</t>
+  </si>
+  <si>
+    <t>Brute forcing OTP verification codes on login</t>
+  </si>
+  <si>
+    <t>Max verification attempt limits check</t>
+  </si>
+  <si>
+    <t>Verify that the backend locks the OTP verification flow after 5 failed attempts to prevent automated code guessing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-015</t>
+  </si>
+  <si>
+    <t>Submitting verification codes that have expired</t>
+  </si>
+  <si>
+    <t>OTP lifespan expiration timers check</t>
+  </si>
+  <si>
+    <t>Verify that verification codes are valid for a maximum of 10 minutes before expiring and being deleted.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-016</t>
+  </si>
+  <si>
+    <t>Flooding SMTP channels by clicking resend code</t>
+  </si>
+  <si>
+    <t>OTP resend cooldown timer check</t>
+  </si>
+  <si>
+    <t>Verify that resending verification codes is locked for 60 seconds after dispatch to prevent mail server abuse.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-017</t>
+  </si>
+  <si>
+    <t>Guessing password reset tokens on forgot password routes</t>
+  </si>
+  <si>
+    <t>Cryptographically secure random reset tokens</t>
+  </si>
+  <si>
+    <t>Verify that password reset tokens use high-entropy random strings to prevent token guessing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-018</t>
+  </si>
+  <si>
+    <t>Submitting a blank registration name field</t>
+  </si>
+  <si>
+    <t>Schema non-empty validation constraints</t>
+  </si>
+  <si>
+    <t>Verify that the signup API rejects empty name inputs with a validation warning.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-019</t>
+  </si>
+  <si>
+    <t>Submitting a blank registration email field</t>
+  </si>
+  <si>
+    <t>Strict email presence validation rules</t>
+  </si>
+  <si>
+    <t>Verify that the signup API rejects empty email inputs with a validation warning.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-020</t>
+  </si>
+  <si>
+    <t>Registering an invalid email format address</t>
+  </si>
+  <si>
+    <t>RFC-compliant email regex validator</t>
+  </si>
+  <si>
+    <t>Verify that the signup API rejects emails that do not conform to standard domain syntax.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-021</t>
+  </si>
+  <si>
+    <t>Bypassing verification by accessing dashboard directly</t>
+  </si>
+  <si>
+    <t>Frontend and Backend route guard checks</t>
+  </si>
+  <si>
+    <t>Verify that the dashboard router rejects non-logged-in users and redirects them to the auth screen.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-022</t>
+  </si>
+  <si>
+    <t>Intercepting session tokens via HTTP referrer links</t>
+  </si>
+  <si>
+    <t>Referrer Policy header integration</t>
+  </si>
+  <si>
+    <t>Verify that API headers set strict referrer policies to prevent token leakage in HTTP headers.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-023</t>
+  </si>
+  <si>
+    <t>Reusing expired password reset links to change access</t>
+  </si>
+  <si>
+    <t>One-time-use password reset tokens</t>
+  </si>
+  <si>
+    <t>Verify that a reset token is marked as used and deleted immediately upon its first execution.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-024</t>
+  </si>
+  <si>
+    <t>Submitting SQL scripts inside login email fields</t>
+  </si>
+  <si>
+    <t>Database parameter binding constraints</t>
+  </si>
+  <si>
+    <t>Verify that database queries treat all inputs as literals, blocking SQL statement injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-025</t>
+  </si>
+  <si>
+    <t>Submitting SQL scripts inside login password fields</t>
+  </si>
+  <si>
+    <t>Database parameter binding validation</t>
+  </si>
+  <si>
+    <t>Verify that password fields are safely parameterized to block SQL injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-026</t>
+  </si>
+  <si>
+    <t>Executing scripts inside token payloads on rendering</t>
+  </si>
+  <si>
+    <t>Client-side template escaping and sanitization</t>
+  </si>
+  <si>
+    <t>Verify that user details inside JWT payloads are escaped before rendering on the screen.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-027</t>
+  </si>
+  <si>
+    <t>Session fixation via predetermined session identifiers</t>
+  </si>
+  <si>
+    <t>Session identifier regeneration on login</t>
+  </si>
+  <si>
+    <t>Verify that the backend generates a completely new session token upon successful credential submission.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-028</t>
+  </si>
+  <si>
+    <t>Bypassing MFA by editing API responses</t>
+  </si>
+  <si>
+    <t>Server-side verification state assertion</t>
+  </si>
+  <si>
+    <t>Verify that the server requires valid session tokens to proceed and does not rely on frontend response flags.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-029</t>
+  </si>
+  <si>
+    <t>Submitting non-numeric codes to verification APIs</t>
+  </si>
+  <si>
+    <t>Strict digit verification filters</t>
+  </si>
+  <si>
+    <t>Verify that the OTP input fields reject alphanumeric characters and enforce 6-digit constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-030</t>
+  </si>
+  <si>
+    <t>Session validation check on connection dropouts</t>
+  </si>
+  <si>
+    <t>Token validation over websocket dropouts</t>
+  </si>
+  <si>
+    <t>Verify that backend routes enforce session validation even when network connections disconnect and reconnect.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-031</t>
+  </si>
+  <si>
+    <t>Brute forcing registration endpoints with fake accounts</t>
+  </si>
+  <si>
+    <t>Registration rate limit rules implementation</t>
+  </si>
+  <si>
+    <t>Verify that the signup API restricts the number of account registrations from a single IP to prevent script abuse.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-032</t>
+  </si>
+  <si>
+    <t>Submitting password change requests without current password</t>
+  </si>
+  <si>
+    <t>Current credential validation requirements</t>
+  </si>
+  <si>
+    <t>Verify that changing the password requires the user to input their existing password successfully.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-033</t>
+  </si>
+  <si>
+    <t>Bypassing password reset validations with empty tokens</t>
+  </si>
+  <si>
+    <t>Token length and structure check</t>
+  </si>
+  <si>
+    <t>Verify that the reset password route rejects empty or null token parameters instantly.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-034</t>
+  </si>
+  <si>
+    <t>Requesting passwords reset link for unregistered email</t>
+  </si>
+  <si>
+    <t>Generic response messaging checks</t>
+  </si>
+  <si>
+    <t>Verify that the reset email endpoint returns a generic success message to prevent user enumeration attacks.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-035</t>
+  </si>
+  <si>
+    <t>Session timeout validation over inactive periods</t>
+  </si>
+  <si>
+    <t>Server-side session expiration rules</t>
+  </si>
+  <si>
+    <t>Verify that the backend checks session age and signs out inactive sessions after a set timeout.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-036</t>
+  </si>
+  <si>
+    <t>Session hijacking via predictable identifiers</t>
+  </si>
+  <si>
+    <t>High-entropy session identifier generation</t>
+  </si>
+  <si>
+    <t>Verify that session IDs are generated using secure random number generators with at least 128 bits of entropy.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-037</t>
+  </si>
+  <si>
+    <t>Exposing active session tokens in log directories</t>
+  </si>
+  <si>
+    <t>Log parameter exclusion filters</t>
+  </si>
+  <si>
+    <t>Verify that logging middlewares strip out tokens and authorization headers from system log outputs.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-038</t>
+  </si>
+  <si>
+    <t>Bypassing email verification checks on registration</t>
+  </si>
+  <si>
+    <t>Account verification state restrictions</t>
+  </si>
+  <si>
+    <t>Verify that unregistered users cannot access dashboard resources before validating their email address.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-039</t>
+  </si>
+  <si>
+    <t>Reusing old tokens after password changes</t>
+  </si>
+  <si>
+    <t>Global token invalidation on credential update</t>
+  </si>
+  <si>
+    <t>Verify that updating a user password invalidates all previously issued JWT tokens.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-040</t>
+  </si>
+  <si>
+    <t>Interfering with registration inputs using Unicode symbols</t>
+  </si>
+  <si>
+    <t>UTF-8 character input normalization</t>
+  </si>
+  <si>
+    <t>Verify that the registration handler normalizes input strings to prevent multi-byte bypass exploits.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-041</t>
+  </si>
+  <si>
+    <t>Bypassing validation checks using local variables</t>
+  </si>
+  <si>
+    <t>Strict API endpoint verification</t>
+  </si>
+  <si>
+    <t>Verify that authentication is verified by the backend on every API call rather than trusting client-side state flags.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-042</t>
+  </si>
+  <si>
+    <t>Accessing resources using tokens signed with weak keys</t>
+  </si>
+  <si>
+    <t>High-entropy HMAC key signature validation</t>
+  </si>
+  <si>
+    <t>Verify that the backend uses a cryptographically secure signature key (minimum 256 bits) to prevent key cracking.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-043</t>
+  </si>
+  <si>
+    <t>Modifying key-id headers in JWT signatures</t>
+  </si>
+  <si>
+    <t>Strict signature key verification whitelist</t>
+  </si>
+  <si>
+    <t>Verify that the token verifier blocks unknown key-id headers to prevent key manipulation attacks.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-044</t>
+  </si>
+  <si>
+    <t>Altering token user identifiers in request query params</t>
+  </si>
+  <si>
+    <t>JWT user identifier context binding</t>
+  </si>
+  <si>
+    <t>Verify that the user context is fetched directly from the verified JWT payload rather than request parameters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-045</t>
+  </si>
+  <si>
+    <t>Re-authenticating requests using cached credentials</t>
+  </si>
+  <si>
+    <t>API routing non-cacheable headers</t>
+  </si>
+  <si>
+    <t>Verify that auth endpoints send headers preventing browsers from caching sensitive authentication screens.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-046</t>
+  </si>
+  <si>
+    <t>Uploading malicious scripts in profile photo formats</t>
+  </si>
+  <si>
+    <t>Strict profile image extension check</t>
+  </si>
+  <si>
+    <t>Verify that the user profile picture API only accepts valid image extensions (.jpg, .jpeg, .png).</t>
+  </si>
+  <si>
+    <t>SEC-VAL-047</t>
+  </si>
+  <si>
+    <t>Injecting custom attributes into signup JSON structures</t>
+  </si>
+  <si>
+    <t>JSON schema strict parsing validations</t>
+  </si>
+  <si>
+    <t>Verify that extra parameters inside signup JSON payloads are stripped and ignored by the controller.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-048</t>
+  </si>
+  <si>
+    <t>Submitting extremely long usernames to crash memory</t>
+  </si>
+  <si>
+    <t>Username field length limitations check</t>
+  </si>
+  <si>
+    <t>Verify that username parameters exceeding 50 characters are rejected with a validation warning.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-049</t>
+  </si>
+  <si>
+    <t>Intercepting session tokens via intermediate proxies</t>
+  </si>
+  <si>
+    <t>Strict TLS certificate validation configuration</t>
+  </si>
+  <si>
+    <t>Verify that connections validate server certificates to prevent man-in-the-middle interception.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-050</t>
+  </si>
+  <si>
+    <t>Accessing endpoints during database connection failures</t>
+  </si>
+  <si>
+    <t>Error wrapper exception handling mechanisms</t>
+  </si>
+  <si>
+    <t>Verify that database connection dropouts return an HTTP 500 without leaking system configurations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-051</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>Reading document records belonging to other users</t>
+  </si>
+  <si>
+    <t>Broken Object Level Authorization checks</t>
+  </si>
+  <si>
+    <t>Verify that requesting a document by ID validates that the owner_id matches the active user session ID.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-052</t>
+  </si>
+  <si>
+    <t>Deleting document records belonging to other accounts</t>
+  </si>
+  <si>
+    <t>Horizontal privilege escalation boundary check</t>
+  </si>
+  <si>
+    <t>Verify that deleting a document by ID validates that the owner_id matches the logged-in user.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-053</t>
+  </si>
+  <si>
+    <t>Updating document metadata owned by other users</t>
+  </si>
+  <si>
+    <t>Strict document ownership update validators</t>
+  </si>
+  <si>
+    <t>Verify that updating a document by ID validates owner permissions before applying database writes.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-054</t>
+  </si>
+  <si>
+    <t>Inviting family members to other family groups</t>
+  </si>
+  <si>
+    <t>Broken Function Level Authorization validations</t>
+  </si>
+  <si>
+    <t>Verify that adding family members validates user family ownership before saving.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-055</t>
+  </si>
+  <si>
+    <t>Deleting member profiles belonging to other families</t>
+  </si>
+  <si>
+    <t>Family member delete authorization rules</t>
+  </si>
+  <si>
+    <t>Verify that deleting a family member card validates user permissions over the target family group.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-056</t>
+  </si>
+  <si>
+    <t>Modifying details of another user's profile card</t>
+  </si>
+  <si>
+    <t>User profile resource ownership checks</t>
+  </si>
+  <si>
+    <t>Verify that editing profile details restricts changes to the active session owner.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-057</t>
+  </si>
+  <si>
+    <t>Accessing administrative dashboard logs directly</t>
+  </si>
+  <si>
+    <t>Role-Based Access Control filters</t>
+  </si>
+  <si>
+    <t>Verify that admin endpoints reject non-admin users with a 403 response.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-058</t>
+  </si>
+  <si>
+    <t>Accessing other users' private file folders via IDOR</t>
+  </si>
+  <si>
+    <t>UUID-based non-enumerable resource keys</t>
+  </si>
+  <si>
+    <t>Verify that the backend uses random UUID strings instead of integers to block folder enumeration.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-059</t>
+  </si>
+  <si>
+    <t>Linking documents to family members of other accounts</t>
+  </si>
+  <si>
+    <t>Foreign key resource validation rule checks</t>
+  </si>
+  <si>
+    <t>Verify that assigning a document to a family member checks that the member belongs to the active account.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-060</t>
+  </si>
+  <si>
+    <t>Accessing backend endpoints without valid authorization headers</t>
+  </si>
+  <si>
+    <t>Strict route-level authentication guards</t>
+  </si>
+  <si>
+    <t>Verify that endpoints reject requests with empty headers.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-061</t>
+  </si>
+  <si>
+    <t>Accessing health check configurations with weak credentials</t>
+  </si>
+  <si>
+    <t>Backend administrator credential requirements</t>
+  </si>
+  <si>
+    <t>Verify that sensitive config checks require valid tokens.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-062</t>
+  </si>
+  <si>
+    <t>Editing files by changing path parameters in API queries</t>
+  </si>
+  <si>
+    <t>Contextual resource lookup authorizations</t>
+  </si>
+  <si>
+    <t>Verify that file retrieval paths are mapped using session database IDs.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-063</t>
+  </si>
+  <si>
+    <t>Accessing shared document links post expiration</t>
+  </si>
+  <si>
+    <t>Shared links expiration datetime checks</t>
+  </si>
+  <si>
+    <t>Verify that signed URLs reject requests when their expiration timestamp has passed.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-064</t>
+  </si>
+  <si>
+    <t>Downloading files from private document folders</t>
+  </si>
+  <si>
+    <t>Supabase storage secure policy integrations</t>
+  </si>
+  <si>
+    <t>Verify that storage objects reject direct download requests without a valid signed URL.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-065</t>
+  </si>
+  <si>
+    <t>Bypassing scopes using custom headers</t>
+  </si>
+  <si>
+    <t>Server-side authorization query rules</t>
+  </si>
+  <si>
+    <t>Verify that administrative roles are checked against the database rather than request header strings.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-066</t>
+  </si>
+  <si>
+    <t>Accessing user settings through API parameters manipulation</t>
+  </si>
+  <si>
+    <t>Strict session-to-user mappings check</t>
+  </si>
+  <si>
+    <t>Verify that user preferences are linked directly to the session user ID.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-067</t>
+  </si>
+  <si>
+    <t>Viewing logs directory folders using direct requests</t>
+  </si>
+  <si>
+    <t>Web server directory index restrictions</t>
+  </si>
+  <si>
+    <t>Verify that requesting directory URLs returns a 403 instead of exposing files list.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-068</t>
+  </si>
+  <si>
+    <t>Inviting administrative users to normal family groups</t>
+  </si>
+  <si>
+    <t>Member role invitation validations</t>
+  </si>
+  <si>
+    <t>Verify that normal users cannot invite admin-level profiles to their families.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-069</t>
+  </si>
+  <si>
+    <t>Removing the owner from a family group account</t>
+  </si>
+  <si>
+    <t>Account owner status protection filters</t>
+  </si>
+  <si>
+    <t>Verify that the backend prevents deleting or removing the primary owner from a family.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-070</t>
+  </si>
+  <si>
+    <t>Modifying document ownership parameters in database</t>
+  </si>
+  <si>
+    <t>Strict document metadata write rules</t>
+  </si>
+  <si>
+    <t>Verify that update document APIs block attempts to modify the user_id foreign key field.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-071</t>
+  </si>
+  <si>
+    <t>Altering database parameters using REST endpoints queries</t>
+  </si>
+  <si>
+    <t>SQL statement query boundaries configuration</t>
+  </si>
+  <si>
+    <t>Verify that API routing logic restricts DB writes to pre-approved model schemas.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-072</t>
+  </si>
+  <si>
+    <t>Accessing configuration tables through public endpoints</t>
+  </si>
+  <si>
+    <t>Private database table permissions config</t>
+  </si>
+  <si>
+    <t>Verify that access to settings database tables is restricted to local systems.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-073</t>
+  </si>
+  <si>
+    <t>Viewing system audit logs without permission credentials</t>
+  </si>
+  <si>
+    <t>Audit trail endpoint access controls</t>
+  </si>
+  <si>
+    <t>Verify that audit APIs validate administrator permissions before exporting data logs.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-074</t>
+  </si>
+  <si>
+    <t>Triggering system backups via unauthorized requests</t>
+  </si>
+  <si>
+    <t>System administrative actions protections</t>
+  </si>
+  <si>
+    <t>Verify that database backup routes require local execution permissions.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-075</t>
+  </si>
+  <si>
+    <t>Restoring database states using modified parameters</t>
+  </si>
+  <si>
+    <t>Strict database restoration command restrictions</t>
+  </si>
+  <si>
+    <t>Verify that database restore APIs block remote requests in production.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-076</t>
+  </si>
+  <si>
+    <t>Accessing development endpoints on production servers</t>
+  </si>
+  <si>
+    <t>Development mode disabled configuration</t>
+  </si>
+  <si>
+    <t>Verify that debugging and development endpoints are disabled in production builds.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-077</t>
+  </si>
+  <si>
+    <t>Executing document parsing APIs from guest sessions</t>
+  </si>
+  <si>
+    <t>Authenticated session gatekeepers integration</t>
+  </si>
+  <si>
+    <t>Verify that document metadata parsing routes reject unauthenticated sessions.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-078</t>
+  </si>
+  <si>
+    <t>Modifying document categorization metadata lists</t>
+  </si>
+  <si>
+    <t>Admin role verification for static assets</t>
+  </si>
+  <si>
+    <t>Verify that editing master categories lists is restricted to system admin accounts.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-079</t>
+  </si>
+  <si>
+    <t>Clearing system warnings from the notification tray</t>
+  </si>
+  <si>
+    <t>Notifications ownership delete checks</t>
+  </si>
+  <si>
+    <t>Verify that deleting alerts validates notification ownership matches the active user.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-080</t>
+  </si>
+  <si>
+    <t>Reading document categories metrics globally</t>
+  </si>
+  <si>
+    <t>User group scope data boundaries check</t>
+  </si>
+  <si>
+    <t>Verify that metrics queries restrict calculations to the active user's data scope.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-081</t>
+  </si>
+  <si>
+    <t>Overwriting security control variables in database</t>
+  </si>
+  <si>
+    <t>Database column write protections config</t>
+  </si>
+  <si>
+    <t>Verify that database writes block modifications to security flag columns.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-082</t>
+  </si>
+  <si>
+    <t>Reading user profile settings by changing context parameters</t>
+  </si>
+  <si>
+    <t>Session matching lookup parameters constraint</t>
+  </si>
+  <si>
+    <t>Verify that profile detail lookups strictly map to verified token attributes.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-083</t>
+  </si>
+  <si>
+    <t>Inviting users from blocked domains to family groups</t>
+  </si>
+  <si>
+    <t>Domain whitelist validation rules</t>
+  </si>
+  <si>
+    <t>Verify that inviting family members checks that their emails belong to whitelisted domains.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-084</t>
+  </si>
+  <si>
+    <t>Deleting logs folders from the local server drive</t>
+  </si>
+  <si>
+    <t>Server file modification restriction policy</t>
+  </si>
+  <si>
+    <t>Verify that system logs directory cannot be modified or deleted via web endpoints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-085</t>
+  </si>
+  <si>
+    <t>Extracting configuration keys from environment setups</t>
+  </si>
+  <si>
+    <t>Environment configs file exposure blocks</t>
+  </si>
+  <si>
+    <t>Verify that web servers block direct requests seeking `.env` configurations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-086</t>
+  </si>
+  <si>
+    <t>Downloading document templates of other families</t>
+  </si>
+  <si>
+    <t>Template ownership access restrictions</t>
+  </si>
+  <si>
+    <t>Verify that downloading custom document templates checks family ownership privileges.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-087</t>
+  </si>
+  <si>
+    <t>Accessing search indexes of other user accounts</t>
+  </si>
+  <si>
+    <t>Search results scope boundary checks</t>
+  </si>
+  <si>
+    <t>Verify that search APIs filter results using the logged-in user's ID.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-088</t>
+  </si>
+  <si>
+    <t>Accessing document metadata logs via direct keys</t>
+  </si>
+  <si>
+    <t>Database query ownership restrictions validation</t>
+  </si>
+  <si>
+    <t>Verify that retrieving document metadata limits outputs to the active account.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-089</t>
+  </si>
+  <si>
+    <t>Adding tags to documents belonging to other users</t>
+  </si>
+  <si>
+    <t>Strict document tag ownership validation rules</t>
+  </si>
+  <si>
+    <t>Verify that appending tag items validates user ownership of the parent document.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-090</t>
+  </si>
+  <si>
+    <t>Clearing session records of other active accounts</t>
+  </si>
+  <si>
+    <t>Session record delete authorization logic</t>
+  </si>
+  <si>
+    <t>Verify that deleting active sessions validates that the session ID belongs to the user.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-091</t>
+  </si>
+  <si>
+    <t>Accessing encryption keys from memory logs</t>
+  </si>
+  <si>
+    <t>Secure memory key management parameters</t>
+  </si>
+  <si>
+    <t>Verify that cryptographic keys are stored in secure memory and never logged.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-092</t>
+  </si>
+  <si>
+    <t>Inviting users to family accounts exceeding max limits</t>
+  </si>
+  <si>
+    <t>Family member count check validation</t>
+  </si>
+  <si>
+    <t>Verify that adding new members checks that the total count does not exceed family plan limits.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-093</t>
+  </si>
+  <si>
+    <t>Accessing document metrics via REST queries parameters</t>
+  </si>
+  <si>
+    <t>Contextual authorization query constraints validation</t>
+  </si>
+  <si>
+    <t>Verify that reporting queries filter parameters using the session token user ID.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-094</t>
+  </si>
+  <si>
+    <t>Downloading bulk ZIP archives of other accounts</t>
+  </si>
+  <si>
+    <t>ZIP builder file ownership validation checks</t>
+  </si>
+  <si>
+    <t>Verify that generating bulk download archives validates ownership of all target document IDs.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-095</t>
+  </si>
+  <si>
+    <t>Accessing temporary uploads directory folder directly</t>
+  </si>
+  <si>
+    <t>Temporary storage directory access permissions</t>
+  </si>
+  <si>
+    <t>Verify that public requests are blocked from listing or downloading from the temporary folder.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-096</t>
+  </si>
+  <si>
+    <t>Triggering notifications dispatch to other users</t>
+  </si>
+  <si>
+    <t>Alert dispatcher channel validation rules</t>
+  </si>
+  <si>
+    <t>Verify that alert APIs restrict notifications target mapping to verified family members.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-097</t>
+  </si>
+  <si>
+    <t>Editing system notifications settings configuration</t>
+  </si>
+  <si>
+    <t>User alert settings database permissions</t>
+  </si>
+  <si>
+    <t>Verify that changing notification rules is restricted to the account owner.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-098</t>
+  </si>
+  <si>
+    <t>Accessing document metadata search parameters options</t>
+  </si>
+  <si>
+    <t>Strict search parameter filters validation checks</t>
+  </si>
+  <si>
+    <t>Verify that search APIs restrict results to active account categories.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-099</t>
+  </si>
+  <si>
+    <t>Deleting system warnings logs files</t>
+  </si>
+  <si>
+    <t>System logs read-only attributes setup</t>
+  </si>
+  <si>
+    <t>Verify that web APIs block delete operations seeking server system log files.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-100</t>
+  </si>
+  <si>
+    <t>Accessing database statistics using client sessions</t>
+  </si>
+  <si>
+    <t>Database query permission restriction setups</t>
+  </si>
+  <si>
+    <t>Verify that normal users cannot execute diagnostic queries on database indexes.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-101</t>
+  </si>
+  <si>
+    <t>Bypassing access controls via HTTP method overriding</t>
+  </si>
+  <si>
+    <t>Strict HTTP method whitelist configurations</t>
+  </si>
+  <si>
+    <t>Verify that routes reject requests specifying modified override headers (e.g. X-HTTP-Method-Override).</t>
+  </si>
+  <si>
+    <t>SEC-VAL-102</t>
+  </si>
+  <si>
+    <t>Accessing server cache directories on local disk</t>
+  </si>
+  <si>
+    <t>Server cache folders read-only constraints</t>
+  </si>
+  <si>
+    <t>Verify that cache data folders are locked from external read requests.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-103</t>
+  </si>
+  <si>
+    <t>Reading backend source code using web controllers</t>
+  </si>
+  <si>
+    <t>Server static file routing boundaries checks</t>
+  </si>
+  <si>
+    <t>Verify that static file routes block path directory parameters seeking source files.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-104</t>
+  </si>
+  <si>
+    <t>Altering database parameters using API URL paths</t>
+  </si>
+  <si>
+    <t>URL parameter database safety constraints</t>
+  </si>
+  <si>
+    <t>Verify that parameter queries only bind values to pre-declared fields.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-105</t>
+  </si>
+  <si>
+    <t>Submitting unauthorized scopes parameters inside JWT</t>
+  </si>
+  <si>
+    <t>Server-side scope validation validations</t>
+  </si>
+  <si>
+    <t>Verify that the server parses and checks roles directly against database status values.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-106</t>
+  </si>
+  <si>
+    <t>Bypassing access controls via headers parameters override</t>
+  </si>
+  <si>
+    <t>Strict headers authentication verification mechanisms</t>
+  </si>
+  <si>
+    <t>Verify that the server validates parameters strictly from the cryptographic token payload.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-107</t>
+  </si>
+  <si>
+    <t>Inviting users with blank names to family accounts</t>
+  </si>
+  <si>
+    <t>Invite parameter presence checks configuration</t>
+  </si>
+  <si>
+    <t>Verify that inviting family members requires entering a valid name string.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-108</t>
+  </si>
+  <si>
+    <t>Retrieving files with modified path parameters</t>
+  </si>
+  <si>
+    <t>Strict path directory structure mapping validation</t>
+  </si>
+  <si>
+    <t>Verify that resource downloads resolve inside defined storage boundaries.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-109</t>
+  </si>
+  <si>
+    <t>Modifying other active users settings profiles</t>
+  </si>
+  <si>
+    <t>Strict record matching validation rules integration</t>
+  </si>
+  <si>
+    <t>Verify that database updates validate active owner credentials before saving.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-110</t>
+  </si>
+  <si>
+    <t>Reading document attachments without security tokens</t>
+  </si>
+  <si>
+    <t>Strict attachments gateway access constraints</t>
+  </si>
+  <si>
+    <t>Verify that fetching files blocks unauthenticated requests with a 401 code.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-111</t>
+  </si>
+  <si>
+    <t>Input Validation</t>
+  </si>
+  <si>
+    <t>SQL Injection via signin email parameter</t>
+  </si>
+  <si>
+    <t>Parameterized database query constraints</t>
+  </si>
+  <si>
+    <t>Verify that email parameters inside auth routes are safely bound to prevent injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-112</t>
+  </si>
+  <si>
+    <t>SQL Injection via signin password parameter</t>
+  </si>
+  <si>
+    <t>Database parameter binding validations check</t>
+  </si>
+  <si>
+    <t>Verify that password parameters inside auth routes are bound safely to prevent injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-113</t>
+  </si>
+  <si>
+    <t>SQL Injection via documents search text queries</t>
+  </si>
+  <si>
+    <t>Strict prepared statement queries execution parameters</t>
+  </si>
+  <si>
+    <t>Verify that entering SQL commands in search parameters treats inputs as literals.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-114</t>
+  </si>
+  <si>
+    <t>SQL Injection via family member name updates input</t>
+  </si>
+  <si>
+    <t>Prepared statement query parameter bindings</t>
+  </si>
+  <si>
+    <t>Verify that family members queries bind text parameters safely to prevent injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-115</t>
+  </si>
+  <si>
+    <t>SQL Injection via registration phone inputs parameters</t>
+  </si>
+  <si>
+    <t>Database driver prepared statement configurations</t>
+  </si>
+  <si>
+    <t>Verify that phone parameters are bound as standard query values to block exploits.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-116</t>
+  </si>
+  <si>
+    <t>SQL Injection via category parameters query parameters</t>
+  </si>
+  <si>
+    <t>Strict input parameter enumerations validation checks</t>
+  </si>
+  <si>
+    <t>SEC-VAL-117</t>
+  </si>
+  <si>
+    <t>SQL Injection via tags update array parameters</t>
+  </si>
+  <si>
+    <t>Safe array input ORM query constraints</t>
+  </si>
+  <si>
+    <t>SEC-VAL-118</t>
+  </si>
+  <si>
+    <t>SQL Injection via document ID route parameters</t>
+  </si>
+  <si>
+    <t>UUID pattern route validation constraints</t>
+  </si>
+  <si>
+    <t>SEC-VAL-119</t>
+  </si>
+  <si>
+    <t>SQL Injection via notifications filter queries parameters</t>
+  </si>
+  <si>
+    <t>Database prepared statements setup verification</t>
+  </si>
+  <si>
+    <t>SEC-VAL-120</t>
+  </si>
+  <si>
+    <t>NoSQL Injection via custom JSON parameters query</t>
+  </si>
+  <si>
+    <t>JSON schema validator parameters filters check</t>
+  </si>
+  <si>
+    <t>Verify that endpoints reject objects containing NoSQL operators (e.g. $gt, $ne).</t>
+  </si>
+  <si>
+    <t>SEC-VAL-121</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document names metadata parameter</t>
+  </si>
+  <si>
+    <t>HTML entities output escaping and sanitization</t>
+  </si>
+  <si>
+    <t>SEC-VAL-122</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member details addresses attributes</t>
+  </si>
+  <si>
+    <t>Strict HTML tags inputs sanitization filters</t>
+  </si>
+  <si>
+    <t>SEC-VAL-123</t>
+  </si>
+  <si>
+    <t>Reflected XSS via categories search filter inputs</t>
+  </si>
+  <si>
+    <t>Sanitized HTTP request parameters rendering rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-124</t>
+  </si>
+  <si>
+    <t>Reflected XSS via notification ID route queries</t>
+  </si>
+  <si>
+    <t>HTML entity output encoding filters integration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-125</t>
+  </si>
+  <si>
+    <t>HTML Injection inside profile names updates parameter</t>
+  </si>
+  <si>
+    <t>HTML tags removal regex filters check</t>
+  </si>
+  <si>
+    <t>SEC-VAL-126</t>
+  </si>
+  <si>
+    <t>System command injection via upload files name attribute</t>
+  </si>
+  <si>
+    <t>Filenames random hash renaming constraints</t>
+  </si>
+  <si>
+    <t>Verify that uploaded files discard original names, preventing command parsing.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-127</t>
+  </si>
+  <si>
+    <t>Directory traversal using null byte parameters injection</t>
+  </si>
+  <si>
+    <t>Binary-safe string filter validation parameters</t>
+  </si>
+  <si>
+    <t>Verify that strings containing null characters are rejected to block path truncation.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-128</t>
+  </si>
+  <si>
+    <t>Directory traversal using boundary path strings (../)</t>
+  </si>
+  <si>
+    <t>Strict path directories boundary resolve limits</t>
+  </si>
+  <si>
+    <t>SEC-VAL-129</t>
+  </si>
+  <si>
+    <t>Buffer overflow via large text fields payloads</t>
+  </si>
+  <si>
+    <t>Schema character limit size constraints</t>
+  </si>
+  <si>
+    <t>SEC-VAL-130</t>
+  </si>
+  <si>
+    <t>Integer overflow via large file size metadata parameters</t>
+  </si>
+  <si>
+    <t>Integer boundary verification parameter checks</t>
+  </si>
+  <si>
+    <t>Verify that file size values are checked to block integer boundary errors.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-131</t>
+  </si>
+  <si>
+    <t>Invalid email syntax during user invitation requests</t>
+  </si>
+  <si>
+    <t>Strict email format constraint regex rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-132</t>
+  </si>
+  <si>
+    <t>Invalid mobile formatting inputs during registration</t>
+  </si>
+  <si>
+    <t>Strict digits validation filter rules configuration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-133</t>
+  </si>
+  <si>
+    <t>Application crash via malformed JSON payload bodies</t>
+  </si>
+  <si>
+    <t>Global custom JSON parsing middleware wrappers</t>
+  </si>
+  <si>
+    <t>SEC-VAL-134</t>
+  </si>
+  <si>
+    <t>Unrestricted file size memory exhaustion checks</t>
+  </si>
+  <si>
+    <t>Upload parser payload size limits configuration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-135</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document tags lists parameter</t>
+  </si>
+  <si>
+    <t>String array element sanitization filters config</t>
+  </si>
+  <si>
+    <t>SEC-VAL-136</t>
+  </si>
+  <si>
+    <t>SQL Injection via custom document sorting parameter</t>
+  </si>
+  <si>
+    <t>Sort parameters whitelist checking verification</t>
+  </si>
+  <si>
+    <t>SEC-VAL-137</t>
+  </si>
+  <si>
+    <t>SQL Injection via profile details address attributes</t>
+  </si>
+  <si>
+    <t>Database statement query parameters execution checks</t>
+  </si>
+  <si>
+    <t>SEC-VAL-138</t>
+  </si>
+  <si>
+    <t>XML External Entity injection via upload streams</t>
+  </si>
+  <si>
+    <t>External entity parsing restrictions validation rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-139</t>
+  </si>
+  <si>
+    <t>System configuration reading via environment paths traversal</t>
+  </si>
+  <si>
+    <t>Path check resolve sandbox boundary verification</t>
+  </si>
+  <si>
+    <t>SEC-VAL-140</t>
+  </si>
+  <si>
+    <t>Input parameter bypass using HTTP Parameter Pollution</t>
+  </si>
+  <si>
+    <t>Strict query parameter object parsing validators</t>
+  </si>
+  <si>
+    <t>SEC-VAL-141</t>
+  </si>
+  <si>
+    <t>Bypassing filters using URL double-encoding variables</t>
+  </si>
+  <si>
+    <t>Safe route parameter decoding filters configurations</t>
+  </si>
+  <si>
+    <t>SEC-VAL-142</t>
+  </si>
+  <si>
+    <t>Uploading batch zip files with directory traversal files</t>
+  </si>
+  <si>
+    <t>ZIP archive unpack path verification checks</t>
+  </si>
+  <si>
+    <t>Verify that zip unpack extract routines block files extracting outside target folders.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-143</t>
+  </si>
+  <si>
+    <t>Bypassing string checks using multi-byte Unicode strings</t>
+  </si>
+  <si>
+    <t>UTF-8 string normalization parameter checks</t>
+  </si>
+  <si>
+    <t>SEC-VAL-144</t>
+  </si>
+  <si>
+    <t>Submitting negative values to array index lookups</t>
+  </si>
+  <si>
+    <t>Index lookup unsigned boundary verification rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-145</t>
+  </si>
+  <si>
+    <t>Application crash via nested JSON object array depth</t>
+  </si>
+  <si>
+    <t>Max JSON parsing depth configuration rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-146</t>
+  </si>
+  <si>
+    <t>Uploading malicious code using document descriptions fields</t>
+  </si>
+  <si>
+    <t>Document text sanitization filter rules integrations</t>
+  </si>
+  <si>
+    <t>Verify that document descriptions strip scripting syntax elements.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-147</t>
+  </si>
+  <si>
+    <t>Bypassing date filters using invalid date formats</t>
+  </si>
+  <si>
+    <t>Strict ISO-8601 date validator validations</t>
+  </si>
+  <si>
+    <t>SEC-VAL-148</t>
+  </si>
+  <si>
+    <t>SQL Injection via document priority flag switch values</t>
+  </si>
+  <si>
+    <t>Boolean input type casting restrictions verification</t>
+  </si>
+  <si>
+    <t>Verify that priority parameters force conversion to boolean data types.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-149</t>
+  </si>
+  <si>
+    <t>Header Injection via custom client information parameters</t>
+  </si>
+  <si>
+    <t>HTTP response header parameters validation rules</t>
+  </si>
+  <si>
+    <t>Verify that client information inputs strip line breaks (CRLF) to prevent header split.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-150</t>
+  </si>
+  <si>
+    <t>Executing local server commands via path injections parameters</t>
+  </si>
+  <si>
+    <t>Safe route mapping constraints validation checks</t>
+  </si>
+  <si>
+    <t>Verify that path parameters resolve using predefined regular expressions.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-151</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document category text fields</t>
+  </si>
+  <si>
+    <t>Strict category parameter sanitization filters config</t>
+  </si>
+  <si>
+    <t>SEC-VAL-152</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member relationship descriptions</t>
+  </si>
+  <si>
+    <t>Family member description sanitization filters config</t>
+  </si>
+  <si>
+    <t>SEC-VAL-153</t>
+  </si>
+  <si>
+    <t>Stored XSS inside notification message fields metadata</t>
+  </si>
+  <si>
+    <t>Strict alert data sanitization checks setup</t>
+  </si>
+  <si>
+    <t>Verify that custom notifications strip tags to prevent script injection.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-154</t>
+  </si>
+  <si>
+    <t>SQL Injection via family member ID route parameters</t>
+  </si>
+  <si>
+    <t>UUID structure route parameter checks configuration</t>
+  </si>
+  <si>
+    <t>Verify that family route endpoints check for valid UUID formatting.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-155</t>
+  </si>
+  <si>
+    <t>SQL Injection via user profile ID route variables</t>
+  </si>
+  <si>
+    <t>Profile route parameters format check validation</t>
+  </si>
+  <si>
+    <t>Verify that profile route parameters reject SQL command parameters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-156</t>
+  </si>
+  <si>
+    <t>Executing command parameters in file metadata parser</t>
+  </si>
+  <si>
+    <t>File parsing parameters validation checks config</t>
+  </si>
+  <si>
+    <t>Verify that reading uploaded file fields strips out command symbols.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-157</t>
+  </si>
+  <si>
+    <t>HTML Injection via document upload source parameters</t>
+  </si>
+  <si>
+    <t>Source tag input sanitization filter parameters</t>
+  </si>
+  <si>
+    <t>SEC-VAL-158</t>
+  </si>
+  <si>
+    <t>Bypassing checks using XML schema external links</t>
+  </si>
+  <si>
+    <t>Parser disabled external references configurations</t>
+  </si>
+  <si>
+    <t>SEC-VAL-159</t>
+  </si>
+  <si>
+    <t>Bypassing database constraints using long blood groups parameters</t>
+  </si>
+  <si>
+    <t>Blood groups category input restriction validations</t>
+  </si>
+  <si>
+    <t>Verify that blood group parameters enforce strict length and string whitelist validation.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-160</t>
+  </si>
+  <si>
+    <t>Injecting script arrays inside tag parameters query</t>
+  </si>
+  <si>
+    <t>String value array validation rules checking</t>
+  </si>
+  <si>
+    <t>Verify that array values check that elements conform to string format constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-161</t>
+  </si>
+  <si>
+    <t>Bypassing string filters using multiple slash characters</t>
+  </si>
+  <si>
+    <t>Strict route normalization filters execution check</t>
+  </si>
+  <si>
+    <t>SEC-VAL-162</t>
+  </si>
+  <si>
+    <t>Accessing folder directories via relative path downloads link</t>
+  </si>
+  <si>
+    <t>Path check resolve directory boundary constraint</t>
+  </si>
+  <si>
+    <t>Verify that file downloads block parameters seeking parent drive folder directories.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-163</t>
+  </si>
+  <si>
+    <t>Executing console actions via query string parameters</t>
+  </si>
+  <si>
+    <t>Endpoint parameters type verification checking</t>
+  </si>
+  <si>
+    <t>SEC-VAL-164</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member notes details</t>
+  </si>
+  <si>
+    <t>Strict notes field sanitization check validation</t>
+  </si>
+  <si>
+    <t>SEC-VAL-165</t>
+  </si>
+  <si>
+    <t>Bypassing date structures using time parameter injections</t>
+  </si>
+  <si>
+    <t>ISO-8601 strict date structure parsing validations</t>
+  </si>
+  <si>
+    <t>SEC-VAL-166</t>
+  </si>
+  <si>
+    <t>SQL Injection via document upload category parameters</t>
+  </si>
+  <si>
+    <t>Strict category code parameters verification constraints</t>
+  </si>
+  <si>
+    <t>SEC-VAL-167</t>
+  </si>
+  <si>
+    <t>Header Injection via custom log headers inputs</t>
+  </si>
+  <si>
+    <t>Safe log formatter header sanitization integration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-168</t>
+  </si>
+  <si>
+    <t>Executing system commands in custom metadata processor</t>
+  </si>
+  <si>
+    <t>Safe processor metadata validation checking rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-169</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document descriptions details fields</t>
+  </si>
+  <si>
+    <t>Description inputs sanitization rules setup configuration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-170</t>
+  </si>
+  <si>
+    <t>Bypassing blood type checks using special characters</t>
+  </si>
+  <si>
+    <t>Strict enum-based blood type checking configuration</t>
+  </si>
+  <si>
+    <t>Verify that blood type updates reject fields that do not match the expected enum patterns.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-171</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member email address fields</t>
+  </si>
+  <si>
+    <t>Strict email input character validations configuration</t>
+  </si>
+  <si>
+    <t>SEC-VAL-172</t>
+  </si>
+  <si>
+    <t>Bypassing numeric limitations using floating point numbers</t>
+  </si>
+  <si>
+    <t>Strict integer type parameter validation configurations</t>
+  </si>
+  <si>
+    <t>SEC-VAL-173</t>
+  </si>
+  <si>
+    <t>Stored XSS inside profile phone number fields details</t>
+  </si>
+  <si>
+    <t>Strict phone validation rules constraints integration</t>
+  </si>
+  <si>
+    <t>Verify that user phone profile data blocks script formatting.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-174</t>
+  </si>
+  <si>
+    <t>SQL Injection via document tag deletion queries</t>
+  </si>
+  <si>
+    <t>Strict tag parameter binding configurations validation</t>
+  </si>
+  <si>
+    <t>SEC-VAL-175</t>
+  </si>
+  <si>
+    <t>Bypassing size constraints using empty parameter keys</t>
+  </si>
+  <si>
+    <t>Schema keys existence check validation rules</t>
+  </si>
+  <si>
+    <t>Verify that requests require required schema properties, blocking null parameter formats.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-176</t>
+  </si>
+  <si>
+    <t>Executing commands in user profile details parsing</t>
+  </si>
+  <si>
+    <t>Strict user profile parser validations checking rules</t>
+  </si>
+  <si>
+    <t>SEC-VAL-177</t>
+  </si>
+  <si>
+    <t>Stored XSS inside document custom category details</t>
+  </si>
+  <si>
+    <t>Strict category text inputs validations parameters</t>
+  </si>
+  <si>
+    <t>SEC-VAL-178</t>
+  </si>
+  <si>
+    <t>Bypassing type constraints using hex-encoded string parameters</t>
+  </si>
+  <si>
+    <t>Strict input decoding boundary constraints checking</t>
+  </si>
+  <si>
+    <t>Verify that hex-encoded inputs are rejected unless explicitly allowed by schema rules.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-179</t>
+  </si>
+  <si>
+    <t>Stored XSS inside family member relationship titles details</t>
+  </si>
+  <si>
+    <t>Relationship titles sanitization filter guidelines configuration</t>
+  </si>
+  <si>
+    <t>Verify that relationship parameters strip out script tags before saving.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-180</t>
+  </si>
+  <si>
+    <t>Bypassing size validation using array representation parameters</t>
+  </si>
+  <si>
+    <t>Strict parameter structure check validation configurations</t>
+  </si>
+  <si>
+    <t>Verify that endpoints validate parameter structure matches expected string type constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-181</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t>Session hijacking via predictable session credentials</t>
+  </si>
+  <si>
+    <t>Cryptographically secure session token generation keys</t>
+  </si>
+  <si>
+    <t>Verify that session identifiers are generated using secure random generators.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-182</t>
+  </si>
+  <si>
+    <t>Reading active cookies from insecure HTTP request logs</t>
+  </si>
+  <si>
+    <t>HTTPS secure connection transport policy rules</t>
+  </si>
+  <si>
+    <t>Verify that backend servers block unencrypted connections and enforce TLS configurations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-183</t>
+  </si>
+  <si>
+    <t>Accessing endpoints post active session deletion request</t>
+  </si>
+  <si>
+    <t>Database session validation verify middlewares config</t>
+  </si>
+  <si>
+    <t>Verify that deleting session records blocks immediate request authentication checks.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-184</t>
+  </si>
+  <si>
+    <t>Altering session structures using query string overrides</t>
+  </si>
+  <si>
+    <t>Strict header credentials lookup constraints configuration</t>
+  </si>
+  <si>
+    <t>Verify that access tokens parse strictly from authorization header fields.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-185</t>
+  </si>
+  <si>
+    <t>Session fixation via predefined cookie structures login</t>
+  </si>
+  <si>
+    <t>Cookie identifier regeneration on credentials success</t>
+  </si>
+  <si>
+    <t>Verify that logging in generates a completely new session identifier.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-186</t>
+  </si>
+  <si>
+    <t>Brute forcing active token payloads values check</t>
+  </si>
+  <si>
+    <t>HMAC-SHA256 signature key verification checks</t>
+  </si>
+  <si>
+    <t>Verify that signature keys enforce 256-bit cryptographical constraints.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-187</t>
+  </si>
+  <si>
+    <t>Accessing resources using cached active sessions index</t>
+  </si>
+  <si>
+    <t>Non-cacheable secure headers routing definitions</t>
+  </si>
+  <si>
+    <t>Verify that endpoints return cache control directives blocking resource storage.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-188</t>
+  </si>
+  <si>
+    <t>Reusing old token credentials after email address update</t>
+  </si>
+  <si>
+    <t>Session invalidation on profile attribute modification</t>
+  </si>
+  <si>
+    <t>Verify that updating user email invalidates current JWT access tokens.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-189</t>
+  </si>
+  <si>
+    <t>Intercepting cookies using proxy request variables modification</t>
+  </si>
+  <si>
+    <t>Secure TLS server credentials configuration verification</t>
+  </si>
+  <si>
+    <t>Verify that TLS connections check server certificate authenticity mappings.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-190</t>
+  </si>
+  <si>
+    <t>Bypassing token validations via algorithm parameters overrides</t>
+  </si>
+  <si>
+    <t>Supported algorithms whitelist checking rules configuration</t>
+  </si>
+  <si>
+    <t>Verify that signature validations reject algorithms that do not match server secret configurations.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-191</t>
+  </si>
+  <si>
+    <t>Accessing pages with expired credentials parameters check</t>
+  </si>
+  <si>
+    <t>Strict credentials lifespan validation checkers</t>
+  </si>
+  <si>
+    <t>Verify that tokens automatically invalidate upon expiration timestamps.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-192</t>
+  </si>
+  <si>
+    <t>Replaying session tokens in multi-tab active states</t>
+  </si>
+  <si>
+    <t>Single session token database lookup verification</t>
+  </si>
+  <si>
+    <t>Verify that sessions match database lookup parameters to prevent token reuse exploits.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-193</t>
+  </si>
+  <si>
+    <t>Altering token attributes inside client cookies variables</t>
+  </si>
+  <si>
+    <t>Strict cookie signature verification guidelines checks</t>
+  </si>
+  <si>
+    <t>Verify that custom cookies check cryptographical signature integrity.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-194</t>
+  </si>
+  <si>
+    <t>Accessing administrative portals using guest active cookies</t>
+  </si>
+  <si>
+    <t>Role mapping permissions check validation rules</t>
+  </si>
+  <si>
+    <t>Verify that portal routes check role permissions before authentication.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-195</t>
+  </si>
+  <si>
+    <t>Injecting characters inside session identifier query string</t>
+  </si>
+  <si>
+    <t>Strict alphanumeric session parsing rules integration</t>
+  </si>
+  <si>
+    <t>Verify that session ID strings conform strictly to alphanumeric formatting rules.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-196</t>
+  </si>
+  <si>
+    <t>Exposing session credentials in web redirection parameters</t>
+  </si>
+  <si>
+    <t>Redirection URI parameter whitelist parameters check</t>
+  </si>
+  <si>
+    <t>Verify that redirects strip token details from address parameters.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-197</t>
+  </si>
+  <si>
+    <t>Bypassing verification checks using local cache databases</t>
+  </si>
+  <si>
+    <t>Server validation on every API endpoint route</t>
+  </si>
+  <si>
+    <t>Verify that access is validated dynamically against active sessions database.</t>
+  </si>
+  <si>
+    <t>SEC-VAL-198</t>
+  </si>
+  <si>
     <t>Accessing resources using tokens signed with insecure keys</t>
   </si>
   <si>
-    <t>HMAC high-entropy key configuration parameters validation checks</t>
+    <t>HMAC high-entropy key configuration parameters validations</t>
   </si>
   <si>
     <t>Verify that JWT signatures use secure keys to prevent key discovery.</t>
   </si>
   <si>
-    <t>SEC-VAL-233</t>
-  </si>
-  <si>
-    <t>Modifying token claims using custom browser setups</t>
-  </si>
-  <si>
-    <t>Cryptographic token integrity verification rules configuration</t>
-  </si>
-  <si>
-    <t>Verify that changing parameters inside token payloads causes decryption errors.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-234</t>
-  </si>
-  <si>
-    <t>Re-authenticating queries using old token storage caches</t>
-  </si>
-  <si>
-    <t>Strict non-cacheable headers parameters validation guidelines</t>
-  </si>
-  <si>
-    <t>Verify that auth endpoints send cache control headers to prevent reuse.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-235</t>
-  </si>
-  <si>
-    <t>Uploading script variables inside profile picture formats</t>
-  </si>
-  <si>
-    <t>File extension mime verification rules configurations checking</t>
-  </si>
-  <si>
-    <t>Verify that user images check for image mime profiles, blocking scripts.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-236</t>
-  </si>
-  <si>
-    <t>Bypassing size constraints using empty payload properties</t>
-  </si>
-  <si>
-    <t>Required parameters structure checking validators integration rules</t>
-  </si>
-  <si>
-    <t>Verify that schemas require non-empty variables to prevent null errors.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-237</t>
-  </si>
-  <si>
-    <t>Executing code inside user profile details addresses</t>
-  </si>
-  <si>
-    <t>Strict user profile inputs sanitization rules integrations checks</t>
-  </si>
-  <si>
-    <t>Verify that address fields strip custom formatting markup before storage.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-238</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document names description fields</t>
-  </si>
-  <si>
-    <t>Strict document metadata text validations parameters checks setup</t>
-  </si>
-  <si>
-    <t>Verify that document names strip tag characters to prevent stored XSS.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-239</t>
-  </si>
-  <si>
-    <t>Bypassing checks using hex-encoded string parameters queries</t>
-  </si>
-  <si>
-    <t>Strict decoding boundary constraint verification check rules guidelines</t>
-  </si>
-  <si>
-    <t>Verify that queries check parameters in original representations to prevent bypass.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-240</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member relationship titles</t>
-  </si>
-  <si>
-    <t>Family relationship text sanitization filter guidelines config rules</t>
-  </si>
-  <si>
-    <t>Verify that family notes strip script tags to block stored XSS.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-241</t>
-  </si>
-  <si>
-    <t>Bypassing checks using multi-byte Unicode parameters fields</t>
-  </si>
-  <si>
-    <t>Character normalization filters validation checking rules config</t>
-  </si>
-  <si>
-    <t>Verify that text parameters normalize Unicode strings to prevent character bypasses.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-242</t>
-  </si>
-  <si>
-    <t>Stored XSS inside notification message fields lists details</t>
-  </si>
-  <si>
-    <t>Notification templates text validation rules constraints integrations checking</t>
-  </si>
-  <si>
-    <t>Verify that notification fields strip tags to block scripting execution.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-243</t>
-  </si>
-  <si>
-    <t>SQL Injection via notification parameters search queries</t>
-  </si>
-  <si>
-    <t>Notification statements prepared query parameter bindings configuration</t>
-  </si>
-  <si>
-    <t>Verify that notification routes parameterize search fields.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-244</t>
-  </si>
-  <si>
-    <t>Executing commands in user profile details inputs</t>
-  </si>
-  <si>
-    <t>Strict profile details parameters sanitization validation rules checks</t>
-  </si>
-  <si>
-    <t>Verify that profile updates strip out shell control characters.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-245</t>
-  </si>
-  <si>
-    <t>HTML Injection via document upload source metadata</t>
-  </si>
-  <si>
-    <t>Source tag parameters input sanitization filters rules checking</t>
-  </si>
-  <si>
-    <t>Verify that document source details discard formatting code.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-246</t>
-  </si>
-  <si>
-    <t>Bypassing checks using XML schema external descriptors</t>
-  </si>
-  <si>
-    <t>Parser disabled external references configurations checking rules</t>
-  </si>
-  <si>
-    <t>Verify that parsing uploads disables processing external schema definitions.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-247</t>
-  </si>
-  <si>
-    <t>Bypassing database constraints using long blood groups values</t>
-  </si>
-  <si>
-    <t>Blood groups category input restriction validations checks config</t>
-  </si>
-  <si>
-    <t>Verify that blood group parameters enforce strict length validations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-248</t>
-  </si>
-  <si>
-    <t>Injecting script arrays inside tag list parameters</t>
-  </si>
-  <si>
-    <t>String value array validation rules checking integrations setup</t>
-  </si>
-  <si>
-    <t>Verify that array values check that elements conform to string constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-249</t>
-  </si>
-  <si>
-    <t>Bypassing string filters using multiple slashes URL</t>
-  </si>
-  <si>
-    <t>Strict route normalization filters execution checks configuration</t>
-  </si>
-  <si>
-    <t>Verify that URL routes normalize double slashes to prevent route path bypassing.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-250</t>
-  </si>
-  <si>
-    <t>Accessing folder directories via relative path downloads query</t>
-  </si>
-  <si>
-    <t>Path check resolve directory boundary constraint checks rules</t>
-  </si>
-  <si>
-    <t>Verify that file downloads block parameters seeking parent drive folders.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-251</t>
-  </si>
-  <si>
-    <t>Executing console actions via query string overrides</t>
-  </si>
-  <si>
-    <t>Endpoint parameters type verification checking guidelines config</t>
-  </si>
-  <si>
-    <t>Verify that API controller methods ignore parameters that do not match expected types.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-252</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member notes metadata</t>
-  </si>
-  <si>
-    <t>Strict notes field sanitization check validation guidelines rules</t>
-  </si>
-  <si>
-    <t>Verify that custom family member notes strip formatting tags before saving.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-253</t>
-  </si>
-  <si>
-    <t>Bypassing date structures using time parameters query</t>
-  </si>
-  <si>
-    <t>ISO-8601 strict date structure parsing validations checking checks</t>
-  </si>
-  <si>
-    <t>Verify that document expiry dates enforce standard date validations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-254</t>
-  </si>
-  <si>
-    <t>SQL Injection via document upload category values</t>
-  </si>
-  <si>
-    <t>Strict category code parameters verification constraints checking config</t>
-  </si>
-  <si>
-    <t>Verify that category inputs restrict values to allowed categories.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-255</t>
-  </si>
-  <si>
-    <t>Header Injection via custom logs formats parameters</t>
-  </si>
-  <si>
-    <t>Safe log formatter header sanitization integration rules checking</t>
-  </si>
-  <si>
-    <t>Verify that values logged from requests are sanitized to prevent log splitting.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-256</t>
-  </si>
-  <si>
-    <t>Executing system commands in custom parser config</t>
-  </si>
-  <si>
-    <t>Safe processor metadata validation checking rules guidelines setup</t>
-  </si>
-  <si>
-    <t>Verify that parser checks block system execution patterns in tags.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-257</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document descriptions text parameters</t>
-  </si>
-  <si>
-    <t>Description inputs sanitization rules setup configuration parameters</t>
-  </si>
-  <si>
-    <t>Verify that custom document description fields strip HTML tag entities.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-258</t>
-  </si>
-  <si>
-    <t>Bypassing blood type checks using special symbols text</t>
-  </si>
-  <si>
-    <t>Strict enum-based blood type checking configuration parameters guidelines</t>
-  </si>
-  <si>
-    <t>Verify that blood type updates reject fields that do not match expected patterns.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-259</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member email inputs parameter</t>
-  </si>
-  <si>
-    <t>Strict email input character validations configuration parameters checking</t>
-  </si>
-  <si>
-    <t>Verify that family email entries check for valid email structures, blocking scripts.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-260</t>
-  </si>
-  <si>
-    <t>Bypassing numeric limitations using float variables inputs</t>
-  </si>
-  <si>
-    <t>Strict integer type parameter validation configurations rules constraints</t>
-  </si>
-  <si>
-    <t>Verify that parameters requiring integer formats reject float values.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-261</t>
-  </si>
-  <si>
-    <t>Stored XSS inside profile phone number entries details</t>
-  </si>
-  <si>
-    <t>Strict phone validation rules constraints integration parameters setup</t>
-  </si>
-  <si>
-    <t>Verify that user phone profile data blocks script formatting.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-262</t>
-  </si>
-  <si>
-    <t>SQL Injection via document tag delete route queries</t>
-  </si>
-  <si>
-    <t>Strict tag parameter binding configurations validation checks rules</t>
-  </si>
-  <si>
-    <t>Verify that deleting tag items parameterizes values safely.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-263</t>
-  </si>
-  <si>
-    <t>Bypassing size constraints using null request parameter keys</t>
-  </si>
-  <si>
-    <t>Schema keys existence check validation rules checking integrations</t>
-  </si>
-  <si>
-    <t>Verify that requests require required schema properties, blocking null formats.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-264</t>
-  </si>
-  <si>
-    <t>Executing commands in user profile metadata details parsing</t>
-  </si>
-  <si>
-    <t>Strict user profile parser validations checking rules parameters checking</t>
-  </si>
-  <si>
-    <t>Verify that profile updates strip system indicators from string variables.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-265</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document custom category selections</t>
-  </si>
-  <si>
-    <t>Strict category text inputs validations parameters checking integration</t>
-  </si>
-  <si>
-    <t>Verify that document category parameters strip tag elements.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-266</t>
-  </si>
-  <si>
-    <t>Bypassing type constraints using hex-encoded request string params</t>
-  </si>
-  <si>
-    <t>Strict input decoding boundary constraints checking parameters validation</t>
-  </si>
-  <si>
-    <t>Verify that hex-encoded inputs are rejected unless allowed by schema rules.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-267</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member relationship categories details</t>
-  </si>
-  <si>
-    <t>Relationship titles sanitization filter guidelines configuration rules constraints</t>
-  </si>
-  <si>
-    <t>Verify that relationship parameters strip out script tags before saving.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-268</t>
-  </si>
-  <si>
-    <t>Bypassing size validation using array representation query params</t>
-  </si>
-  <si>
-    <t>Strict parameter structure check validation configurations rules parameters</t>
-  </si>
-  <si>
-    <t>Verify that endpoints validate parameter structure matches expected string constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-269</t>
-  </si>
-  <si>
-    <t>SQL Injection via document category filter inputs variables</t>
-  </si>
-  <si>
-    <t>Strict input parameter enumerations validation checks rules configuration</t>
-  </si>
-  <si>
-    <t>Verify that category filters match approved enumerations list to prevent SQL injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-270</t>
-  </si>
-  <si>
-    <t>SQL Injection via tags update array parameters queries</t>
-  </si>
-  <si>
-    <t>Safe array input ORM query constraints validation checks parameters</t>
-  </si>
-  <si>
-    <t>Verify that array values inside update queries are parsed as data variables.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-271</t>
-  </si>
-  <si>
-    <t>SQL Injection via document ID route parameters queries</t>
-  </si>
-  <si>
-    <t>UUID pattern route validation constraints checking parameters config</t>
-  </si>
-  <si>
-    <t>Verify that route routes check for UUID formats, blocking injection strings.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-272</t>
-  </si>
-  <si>
-    <t>SQL Injection via notifications filter queries parameters checking</t>
-  </si>
-  <si>
-    <t>Database prepared statements setup verification checks guidelines rules</t>
-  </si>
-  <si>
-    <t>Verify that alert filters parameterize options to prevent SQL injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-273</t>
-  </si>
-  <si>
-    <t>NoSQL Injection via custom JSON parameters query options</t>
-  </si>
-  <si>
-    <t>JSON schema validator parameters filters check parameters rules constraints</t>
-  </si>
-  <si>
-    <t>Verify that endpoints reject objects containing NoSQL operators.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-274</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document names metadata parameter details</t>
-  </si>
-  <si>
-    <t>HTML entities output escaping and sanitization parameters checking rules</t>
-  </si>
-  <si>
-    <t>Verify that custom document names strip out HTML tag symbols before database writes.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-275</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member details addresses attributes parameters</t>
-  </si>
-  <si>
-    <t>Strict HTML tags inputs sanitization filters rules constraints checking</t>
-  </si>
-  <si>
-    <t>Verify that family addresses are sanitized to prevent stored script injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-276</t>
-  </si>
-  <si>
-    <t>Reflected XSS via categories search filter inputs variables</t>
-  </si>
-  <si>
-    <t>Sanitized HTTP request parameters rendering rules checking guidelines config</t>
-  </si>
-  <si>
-    <t>Verify that search values are encoded before rendering in application logs.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-277</t>
-  </si>
-  <si>
-    <t>Reflected XSS via notification ID route queries options</t>
-  </si>
-  <si>
-    <t>HTML entity output encoding filters integration parameters check rules</t>
-  </si>
-  <si>
-    <t>Verify that notification lookups validate inputs before processing search variables.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-278</t>
-  </si>
-  <si>
-    <t>HTML Injection inside profile names updates parameter variables</t>
-  </si>
-  <si>
-    <t>HTML tags removal regex filters check parameters validation rules</t>
-  </si>
-  <si>
-    <t>Verify that profile names discard tag parameters to block rendering manipulation.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-279</t>
-  </si>
-  <si>
-    <t>System command injection via upload files name attribute options</t>
-  </si>
-  <si>
-    <t>Filenames random hash renaming constraints rules parameters checking</t>
-  </si>
-  <si>
-    <t>Verify that uploaded files discard original names, preventing command parsing.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-280</t>
-  </si>
-  <si>
-    <t>Directory traversal using null byte parameters injection details</t>
-  </si>
-  <si>
-    <t>Binary-safe string filter validation parameters rules constraints checking</t>
-  </si>
-  <si>
-    <t>Verify that strings containing null characters are rejected to block path truncation.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-281</t>
-  </si>
-  <si>
-    <t>Directory traversal using boundary path strings details</t>
-  </si>
-  <si>
-    <t>Strict path directories boundary resolve limits checking rules parameters</t>
-  </si>
-  <si>
-    <t>Verify that relative path indicators are stripped from file search queries.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-282</t>
-  </si>
-  <si>
-    <t>Buffer overflow via large text fields payloads variables</t>
-  </si>
-  <si>
-    <t>Schema character limit size constraints rules checking configurations</t>
-  </si>
-  <si>
-    <t>Verify that database fields reject strings exceeding column width declarations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-283</t>
-  </si>
-  <si>
-    <t>Integer overflow via large file size metadata parameters options</t>
-  </si>
-  <si>
-    <t>Integer boundary verification parameter checks rules parameters validation</t>
-  </si>
-  <si>
-    <t>Verify that file size values are checked to block integer boundary errors.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-284</t>
-  </si>
-  <si>
-    <t>Invalid email syntax during user invitation requests details</t>
-  </si>
-  <si>
-    <t>Strict email format constraint regex rules constraints checking parameters</t>
-  </si>
-  <si>
-    <t>Verify that invites block emails lacking proper domain and suffix formats.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-285</t>
-  </si>
-  <si>
-    <t>Invalid mobile formatting inputs during registration options</t>
-  </si>
-  <si>
-    <t>Strict digits validation filter rules configuration parameters checking rules</t>
-  </si>
-  <si>
-    <t>Verify that mobile inputs reject letters and enforce 10-digit constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-286</t>
-  </si>
-  <si>
-    <t>Application crash via malformed JSON payload bodies variables</t>
-  </si>
-  <si>
-    <t>Global custom JSON parsing middleware wrappers checking rules parameters</t>
-  </si>
-  <si>
-    <t>Verify that invalid JSON formatting returns a 400 instead of crashing processes.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-287</t>
-  </si>
-  <si>
-    <t>Unrestricted file size memory exhaustion checks options</t>
-  </si>
-  <si>
-    <t>Upload parser payload size limits configuration parameters rules checking</t>
-  </si>
-  <si>
-    <t>Verify that uploads reject files larger than 10MB to prevent resource starvation.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-288</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document tags lists parameter details</t>
-  </si>
-  <si>
-    <t>String array element sanitization filters config rules checking integrations</t>
-  </si>
-  <si>
-    <t>Verify that array fields sanitize each element before database insertion.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-289</t>
-  </si>
-  <si>
-    <t>SQL Injection via custom document sorting parameter queries</t>
-  </si>
-  <si>
-    <t>Sort parameters whitelist checking verification parameters checking guidelines</t>
-  </si>
-  <si>
-    <t>Verify that order-by inputs validate against allowed column keys list.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-290</t>
-  </si>
-  <si>
-    <t>SQL Injection via profile details address attributes queries</t>
-  </si>
-  <si>
-    <t>Database statement query parameters execution checks rules validation checking</t>
-  </si>
-  <si>
-    <t>Verify that profile updates parameterize address values safely.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-291</t>
-  </si>
-  <si>
-    <t>XML External Entity injection via upload streams details</t>
-  </si>
-  <si>
-    <t>External entity parsing restrictions validation rules constraints checking parameter</t>
-  </si>
-  <si>
-    <t>Verify that XML parsers reject external entity references to prevent file reading.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-292</t>
-  </si>
-  <si>
-    <t>System configuration reading via environment paths traversal variables</t>
-  </si>
-  <si>
-    <t>Path check resolve sandbox boundary verification rules checking parameters</t>
-  </si>
-  <si>
-    <t>Verify that path parameters block attempts to access system config directories.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-293</t>
-  </si>
-  <si>
-    <t>Input parameter bypass using HTTP Parameter Pollution options</t>
-  </si>
-  <si>
-    <t>Strict query parameter object parsing validators parameters rules constraints</t>
-  </si>
-  <si>
-    <t>Verify that duplicate query parameters are processed as a single string.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-294</t>
-  </si>
-  <si>
-    <t>Bypassing filters using URL double-encoding variables details</t>
-  </si>
-  <si>
-    <t>Safe route parameter decoding filters configurations parameters checking rules</t>
-  </si>
-  <si>
-    <t>Verify that route parameters decode safely to prevent filters bypass.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-295</t>
-  </si>
-  <si>
-    <t>Uploading batch zip files with directory traversal files options</t>
-  </si>
-  <si>
-    <t>ZIP archive unpack path verification checks rules parameters checking rules</t>
-  </si>
-  <si>
-    <t>Verify that zip unpack extract routines block files extracting outside target folders.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-296</t>
-  </si>
-  <si>
-    <t>Bypassing string checks using multi-byte Unicode strings variables</t>
-  </si>
-  <si>
-    <t>UTF-8 string normalization parameter checks rules checking configurations parameters</t>
-  </si>
-  <si>
-    <t>Verify that text parser normalizes string symbols to prevent character bypasses.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-297</t>
-  </si>
-  <si>
-    <t>Submitting negative values to array index lookups details</t>
-  </si>
-  <si>
-    <t>Index lookup unsigned boundary verification rules constraints checking parameters</t>
-  </si>
-  <si>
-    <t>Verify that database offsets require positive integer formats.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-298</t>
-  </si>
-  <si>
-    <t>Application crash via nested JSON object array depth variables</t>
-  </si>
-  <si>
-    <t>Max JSON parsing depth configuration rules checking configurations parameters validation</t>
-  </si>
-  <si>
-    <t>Verify that JSON parser rejects objects exceeding 20 levels of nesting depth.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-299</t>
-  </si>
-  <si>
-    <t>Uploading malicious code using document descriptions fields details</t>
-  </si>
-  <si>
-    <t>Document text sanitization filter rules integrations constraints checking parameters</t>
-  </si>
-  <si>
-    <t>Verify that document description fields strip scripting syntax.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-300</t>
-  </si>
-  <si>
-    <t>Bypassing date structures using invalid date formats options</t>
-  </si>
-  <si>
-    <t>Strict ISO-8601 date validator validations parameters checking rules constraints</t>
-  </si>
-  <si>
-    <t>Verify that date-based query filters reject malformed date representations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-301</t>
-  </si>
-  <si>
-    <t>SQL Injection via document priority flag switch values queries</t>
-  </si>
-  <si>
-    <t>Boolean input type casting restrictions verification checks guidelines rules parameters</t>
-  </si>
-  <si>
-    <t>Verify that priority parameters force conversion to boolean data types.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-302</t>
-  </si>
-  <si>
-    <t>Header Injection via custom client information parameters options</t>
-  </si>
-  <si>
-    <t>HTTP response header parameters validation rules constraints parameters checking</t>
-  </si>
-  <si>
-    <t>Verify that client information inputs strip line breaks (CRLF) to prevent header split.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-303</t>
-  </si>
-  <si>
-    <t>Executing local server commands via path injections parameters details</t>
-  </si>
-  <si>
-    <t>Safe route mapping constraints validation checks rules parameters checking validation</t>
-  </si>
-  <si>
-    <t>Verify that path parameters resolve using predefined regular expressions.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-304</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document category text fields options</t>
-  </si>
-  <si>
-    <t>Strict category parameter sanitization filters config rules checking parameters checking</t>
-  </si>
-  <si>
-    <t>Verify that category inputs block custom script injections.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-305</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member relationship descriptions variables</t>
-  </si>
-  <si>
-    <t>Family member description sanitization filters config rules checking configurations limits</t>
-  </si>
-  <si>
-    <t>Verify that relationship parameters strip out script tags before storage.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-001</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Brute-force password guessing attacks on login form</t>
-  </si>
-  <si>
-    <t>Express Rate Limit middleware on auth routes</t>
-  </si>
-  <si>
-    <t>Verify that successive failed login attempts from a single IP address trigger a temporary lockout to prevent credential brute forcing.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-002</t>
-  </si>
-  <si>
-    <t>Storage of plain-text passwords in database</t>
-  </si>
-  <si>
-    <t>Bcrypt cryptographic hashing with salt rounds</t>
-  </si>
-  <si>
-    <t>Verify that user passwords are encrypted using bcrypt before being written to the users database table.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-003</t>
-  </si>
-  <si>
-    <t>Setting weak or short passwords during registration</t>
-  </si>
-  <si>
-    <t>Backend password length threshold checker</t>
-  </si>
-  <si>
-    <t>Verify that the signup API rejects password entries shorter than 6 characters with a validation error.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-004</t>
-  </si>
-  <si>
-    <t>Registering multiple accounts with the same email</t>
-  </si>
-  <si>
-    <t>Unique database index on email column</t>
-  </si>
-  <si>
-    <t>Verify that the registration service blocks duplicate signups for the same email address, returning a 409 status.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-005</t>
-  </si>
-  <si>
-    <t>Accessing secure endpoints using an expired JWT token</t>
-  </si>
-  <si>
-    <t>Token expiration timestamp validation</t>
-  </si>
-  <si>
-    <t>Verify that the gateway rejects tokens that have passed their exp timestamp and returns a 401 response.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-006</t>
-  </si>
-  <si>
-    <t>Bypassing signatures by stripping cryptographic hashes</t>
-  </si>
-  <si>
-    <t>Strict JWT signature verification rules</t>
-  </si>
-  <si>
-    <t>Verify that the server blocks tokens whose signature portion has been altered or omitted completely.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-007</t>
-  </si>
-  <si>
-    <t>Bypassing signatures by changing algorithm to none</t>
-  </si>
-  <si>
-    <t>Algorithm whitelist constraint validation</t>
-  </si>
-  <si>
-    <t>Verify that JWT libraries explicitly reject tokens specifying "none" in the header algorithm parameters.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-008</t>
-  </si>
-  <si>
-    <t>Replaying session tokens after a logout request</t>
-  </si>
-  <si>
-    <t>Server-side token validation lookup</t>
-  </si>
-  <si>
-    <t>Verify that calling logout invalidates the active session identifier so the token cannot be reused.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-009</t>
-  </si>
-  <si>
-    <t>Intercepting session cookies over unencrypted HTTP</t>
-  </si>
-  <si>
-    <t>Secure flag cookie attributes configuration</t>
-  </si>
-  <si>
-    <t>Verify that the server only transmits authentication cookies over encrypted HTTPS channels.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-010</t>
-  </si>
-  <si>
-    <t>Reading session cookies using malicious browser scripts</t>
-  </si>
-  <si>
-    <t>HttpOnly flag cookie attributes configuration</t>
-  </si>
-  <si>
-    <t>Verify that cookies are set with the HttpOnly flag to prevent XSS scripts from reading session identifiers.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-011</t>
-  </si>
-  <si>
-    <t>Cross-Site Request Forgery cookie submissions</t>
-  </si>
-  <si>
-    <t>SameSite=Lax cookie attribute enforcement</t>
-  </si>
-  <si>
-    <t>Verify that authentication cookies enforce SameSite attributes to block cross-site script request forgeries.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-012</t>
-  </si>
-  <si>
-    <t>Accessing resources without any authorization header</t>
-  </si>
-  <si>
-    <t>Authentication check gateway middleware</t>
-  </si>
-  <si>
-    <t>Verify that requesting protected backend resources without a token returns a 401 unauthorized status.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-013</t>
-  </si>
-  <si>
-    <t>Modifying claims inside the token to escalate roles</t>
-  </si>
-  <si>
-    <t>Token payload integrity validations</t>
-  </si>
-  <si>
-    <t>Verify that changes to the payload parameters of a JWT are detected and rejected by signature verification.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-014</t>
-  </si>
-  <si>
-    <t>Brute forcing OTP verification codes on login</t>
-  </si>
-  <si>
-    <t>Max verification attempt limits check</t>
-  </si>
-  <si>
-    <t>Verify that the backend locks the OTP verification flow after 5 failed attempts to prevent automated code guessing.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-015</t>
-  </si>
-  <si>
-    <t>Submitting verification codes that have expired</t>
-  </si>
-  <si>
-    <t>OTP lifespan expiration timers check</t>
-  </si>
-  <si>
-    <t>Verify that verification codes are valid for a maximum of 10 minutes before expiring and being deleted.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-016</t>
-  </si>
-  <si>
-    <t>Flooding SMTP channels by clicking resend code</t>
-  </si>
-  <si>
-    <t>OTP resend cooldown timer check</t>
-  </si>
-  <si>
-    <t>Verify that resending verification codes is locked for 60 seconds after dispatch to prevent mail server abuse.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-017</t>
-  </si>
-  <si>
-    <t>Guessing password reset tokens on forgot password routes</t>
-  </si>
-  <si>
-    <t>Cryptographically secure random reset tokens</t>
-  </si>
-  <si>
-    <t>Verify that password reset tokens use high-entropy random strings to prevent token guessing.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-018</t>
-  </si>
-  <si>
-    <t>Submitting a blank registration name field</t>
-  </si>
-  <si>
-    <t>Schema non-empty validation constraints</t>
-  </si>
-  <si>
-    <t>Verify that the signup API rejects empty name inputs with a validation warning.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-019</t>
-  </si>
-  <si>
-    <t>Submitting a blank registration email field</t>
-  </si>
-  <si>
-    <t>Strict email presence validation rules</t>
-  </si>
-  <si>
-    <t>Verify that the signup API rejects empty email inputs with a validation warning.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-020</t>
-  </si>
-  <si>
-    <t>Registering an invalid email format address</t>
-  </si>
-  <si>
-    <t>RFC-compliant email regex validator</t>
-  </si>
-  <si>
-    <t>Verify that the signup API rejects emails that do not conform to standard domain syntax.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-021</t>
-  </si>
-  <si>
-    <t>Bypassing verification by accessing dashboard directly</t>
-  </si>
-  <si>
-    <t>Frontend and Backend route guard checks</t>
-  </si>
-  <si>
-    <t>Verify that the dashboard router rejects non-logged-in users and redirects them to the auth screen.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-022</t>
-  </si>
-  <si>
-    <t>Intercepting session tokens via HTTP referrer links</t>
-  </si>
-  <si>
-    <t>Referrer Policy header integration</t>
-  </si>
-  <si>
-    <t>Verify that API headers set strict referrer policies to prevent token leakage in HTTP headers.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-023</t>
-  </si>
-  <si>
-    <t>Reusing expired password reset links to change access</t>
-  </si>
-  <si>
-    <t>One-time-use password reset tokens</t>
-  </si>
-  <si>
-    <t>Verify that a reset token is marked as used and deleted immediately upon its first execution.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-024</t>
-  </si>
-  <si>
-    <t>Submitting SQL scripts inside login email fields</t>
-  </si>
-  <si>
-    <t>Database parameter binding constraints</t>
-  </si>
-  <si>
-    <t>Verify that database queries treat all inputs as literals, blocking SQL statement injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-025</t>
-  </si>
-  <si>
-    <t>Submitting SQL scripts inside login password fields</t>
-  </si>
-  <si>
-    <t>Database parameter binding validation</t>
-  </si>
-  <si>
-    <t>Verify that password fields are safely parameterized to block SQL injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-026</t>
-  </si>
-  <si>
-    <t>Executing scripts inside token payloads on rendering</t>
-  </si>
-  <si>
-    <t>Client-side template escaping and sanitization</t>
-  </si>
-  <si>
-    <t>Verify that user details inside JWT payloads are escaped before rendering on the screen.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-027</t>
-  </si>
-  <si>
-    <t>Session fixation via predetermined session identifiers</t>
-  </si>
-  <si>
-    <t>Session identifier regeneration on login</t>
-  </si>
-  <si>
-    <t>Verify that the backend generates a completely new session token upon successful credential submission.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-028</t>
-  </si>
-  <si>
-    <t>Bypassing MFA by editing API responses</t>
-  </si>
-  <si>
-    <t>Server-side verification state assertion</t>
-  </si>
-  <si>
-    <t>Verify that the server requires valid session tokens to proceed and does not rely on frontend response flags.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-029</t>
-  </si>
-  <si>
-    <t>Submitting non-numeric codes to verification APIs</t>
-  </si>
-  <si>
-    <t>Strict digit verification filters</t>
-  </si>
-  <si>
-    <t>Verify that the OTP input fields reject alphanumeric characters and enforce 6-digit constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-030</t>
-  </si>
-  <si>
-    <t>Session validation check on connection dropouts</t>
-  </si>
-  <si>
-    <t>Token validation over websocket dropouts</t>
-  </si>
-  <si>
-    <t>Verify that backend routes enforce session validation even when network connections disconnect and reconnect.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-031</t>
-  </si>
-  <si>
-    <t>Brute forcing registration endpoints with fake accounts</t>
-  </si>
-  <si>
-    <t>Registration rate limit rules implementation</t>
-  </si>
-  <si>
-    <t>Verify that the signup API restricts the number of account registrations from a single IP to prevent script abuse.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-032</t>
-  </si>
-  <si>
-    <t>Submitting password change requests without current password</t>
-  </si>
-  <si>
-    <t>Current credential validation requirements</t>
-  </si>
-  <si>
-    <t>Verify that changing the password requires the user to input their existing password successfully.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-033</t>
-  </si>
-  <si>
-    <t>Bypassing password reset validations with empty tokens</t>
-  </si>
-  <si>
-    <t>Token length and structure check</t>
-  </si>
-  <si>
-    <t>Verify that the reset password route rejects empty or null token parameters instantly.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-034</t>
-  </si>
-  <si>
-    <t>Requesting passwords reset link for unregistered email</t>
-  </si>
-  <si>
-    <t>Generic response messaging checks</t>
-  </si>
-  <si>
-    <t>Verify that the reset email endpoint returns a generic success message to prevent user enumeration attacks.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-035</t>
-  </si>
-  <si>
-    <t>Session timeout validation over inactive periods</t>
-  </si>
-  <si>
-    <t>Server-side session expiration rules</t>
-  </si>
-  <si>
-    <t>Verify that the backend checks session age and signs out inactive sessions after a set timeout.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-036</t>
-  </si>
-  <si>
-    <t>Session hijacking via predictable identifiers</t>
-  </si>
-  <si>
-    <t>High-entropy session identifier generation</t>
-  </si>
-  <si>
-    <t>Verify that session IDs are generated using secure random number generators with at least 128 bits of entropy.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-037</t>
-  </si>
-  <si>
-    <t>Exposing active session tokens in log directories</t>
-  </si>
-  <si>
-    <t>Log parameter exclusion filters</t>
-  </si>
-  <si>
-    <t>Verify that logging middlewares strip out tokens and authorization headers from system log outputs.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-038</t>
-  </si>
-  <si>
-    <t>Bypassing email verification checks on registration</t>
-  </si>
-  <si>
-    <t>Account verification state restrictions</t>
-  </si>
-  <si>
-    <t>Verify that unregistered users cannot access dashboard resources before validating their email address.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-039</t>
-  </si>
-  <si>
-    <t>Reusing old tokens after password changes</t>
-  </si>
-  <si>
-    <t>Global token invalidation on credential update</t>
-  </si>
-  <si>
-    <t>Verify that updating a user password invalidates all previously issued JWT tokens.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-040</t>
-  </si>
-  <si>
-    <t>Interfering with registration inputs using Unicode symbols</t>
-  </si>
-  <si>
-    <t>UTF-8 character input normalization</t>
-  </si>
-  <si>
-    <t>Verify that the registration handler normalizes input strings to prevent multi-byte bypass exploits.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-041</t>
-  </si>
-  <si>
-    <t>Bypassing validation checks using local variables</t>
-  </si>
-  <si>
-    <t>Strict API endpoint verification</t>
-  </si>
-  <si>
-    <t>Verify that authentication is verified by the backend on every API call rather than trusting client-side state flags.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-042</t>
-  </si>
-  <si>
-    <t>Accessing resources using tokens signed with weak keys</t>
-  </si>
-  <si>
-    <t>High-entropy HMAC key signature validation</t>
-  </si>
-  <si>
-    <t>Verify that the backend uses a cryptographically secure signature key (minimum 256 bits) to prevent key cracking.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-043</t>
-  </si>
-  <si>
-    <t>Modifying key-id headers in JWT signatures</t>
-  </si>
-  <si>
-    <t>Strict signature key verification whitelist</t>
-  </si>
-  <si>
-    <t>Verify that the token verifier blocks unknown key-id headers to prevent key manipulation attacks.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-044</t>
-  </si>
-  <si>
-    <t>Altering token user identifiers in request query params</t>
-  </si>
-  <si>
-    <t>JWT user identifier context binding</t>
-  </si>
-  <si>
-    <t>Verify that the user context is fetched directly from the verified JWT payload rather than request parameters.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-045</t>
-  </si>
-  <si>
-    <t>Re-authenticating requests using cached credentials</t>
-  </si>
-  <si>
-    <t>API routing non-cacheable headers</t>
-  </si>
-  <si>
-    <t>Verify that auth endpoints send headers preventing browsers from caching sensitive authentication screens.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-046</t>
-  </si>
-  <si>
-    <t>Uploading malicious scripts in profile photo formats</t>
-  </si>
-  <si>
-    <t>Strict profile image extension check</t>
-  </si>
-  <si>
-    <t>Verify that the user profile picture API only accepts valid image extensions (.jpg, .jpeg, .png).</t>
-  </si>
-  <si>
-    <t>SEC-VAL-047</t>
-  </si>
-  <si>
-    <t>Injecting custom attributes into signup JSON structures</t>
-  </si>
-  <si>
-    <t>JSON schema strict parsing validations</t>
-  </si>
-  <si>
-    <t>Verify that extra parameters inside signup JSON payloads are stripped and ignored by the controller.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-048</t>
-  </si>
-  <si>
-    <t>Submitting extremely long usernames to crash memory</t>
-  </si>
-  <si>
-    <t>Username field length limitations check</t>
-  </si>
-  <si>
-    <t>Verify that username parameters exceeding 50 characters are rejected with a validation warning.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-049</t>
-  </si>
-  <si>
-    <t>Intercepting session tokens via intermediate proxies</t>
-  </si>
-  <si>
-    <t>Strict TLS certificate validation configuration</t>
-  </si>
-  <si>
-    <t>Verify that connections validate server certificates to prevent man-in-the-middle interception.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-050</t>
-  </si>
-  <si>
-    <t>Accessing endpoints during database connection failures</t>
-  </si>
-  <si>
-    <t>Error wrapper exception handling mechanisms</t>
-  </si>
-  <si>
-    <t>Verify that database connection dropouts return an HTTP 500 without leaking system configurations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-051</t>
-  </si>
-  <si>
-    <t>Authorization</t>
-  </si>
-  <si>
-    <t>Reading document records belonging to other users</t>
-  </si>
-  <si>
-    <t>Broken Object Level Authorization checks</t>
-  </si>
-  <si>
-    <t>Verify that requesting a document by ID validates that the owner_id matches the active user session ID.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-052</t>
-  </si>
-  <si>
-    <t>Deleting document records belonging to other accounts</t>
-  </si>
-  <si>
-    <t>Horizontal privilege escalation boundary check</t>
-  </si>
-  <si>
-    <t>Verify that deleting a document by ID validates that the owner_id matches the logged-in user.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-053</t>
-  </si>
-  <si>
-    <t>Updating document metadata owned by other users</t>
-  </si>
-  <si>
-    <t>Strict document ownership update validators</t>
-  </si>
-  <si>
-    <t>Verify that updating a document by ID validates owner permissions before applying database writes.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-054</t>
-  </si>
-  <si>
-    <t>Inviting family members to other family groups</t>
-  </si>
-  <si>
-    <t>Broken Function Level Authorization validations</t>
-  </si>
-  <si>
-    <t>Verify that adding family members validates user family ownership before saving.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-055</t>
-  </si>
-  <si>
-    <t>Deleting member profiles belonging to other families</t>
-  </si>
-  <si>
-    <t>Family member delete authorization rules</t>
-  </si>
-  <si>
-    <t>Verify that deleting a family member card validates user permissions over the target family group.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-056</t>
-  </si>
-  <si>
-    <t>Modifying details of another user's profile card</t>
-  </si>
-  <si>
-    <t>User profile resource ownership checks</t>
-  </si>
-  <si>
-    <t>Verify that editing profile details restricts changes to the active session owner.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-057</t>
-  </si>
-  <si>
-    <t>Accessing administrative dashboard logs directly</t>
-  </si>
-  <si>
-    <t>Role-Based Access Control filters</t>
-  </si>
-  <si>
-    <t>Verify that admin endpoints reject non-admin users with a 403 response.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-058</t>
-  </si>
-  <si>
-    <t>Accessing other users' private file folders via IDOR</t>
-  </si>
-  <si>
-    <t>UUID-based non-enumerable resource keys</t>
-  </si>
-  <si>
-    <t>Verify that the backend uses random UUID strings instead of integers to block folder enumeration.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-059</t>
-  </si>
-  <si>
-    <t>Linking documents to family members of other accounts</t>
-  </si>
-  <si>
-    <t>Foreign key resource validation rule checks</t>
-  </si>
-  <si>
-    <t>Verify that assigning a document to a family member checks that the member belongs to the active account.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-060</t>
-  </si>
-  <si>
-    <t>Accessing backend endpoints without valid authorization headers</t>
-  </si>
-  <si>
-    <t>Strict route-level authentication guards</t>
-  </si>
-  <si>
-    <t>Verify that endpoints reject requests with empty headers.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-061</t>
-  </si>
-  <si>
-    <t>Accessing health check configurations with weak credentials</t>
-  </si>
-  <si>
-    <t>Backend administrator credential requirements</t>
-  </si>
-  <si>
-    <t>Verify that sensitive config checks require valid tokens.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-062</t>
-  </si>
-  <si>
-    <t>Editing files by changing path parameters in API queries</t>
-  </si>
-  <si>
-    <t>Contextual resource lookup authorizations</t>
-  </si>
-  <si>
-    <t>Verify that file retrieval paths are mapped using session database IDs.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-063</t>
-  </si>
-  <si>
-    <t>Accessing shared document links post expiration</t>
-  </si>
-  <si>
-    <t>Shared links expiration datetime checks</t>
-  </si>
-  <si>
-    <t>Verify that signed URLs reject requests when their expiration timestamp has passed.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-064</t>
-  </si>
-  <si>
-    <t>Downloading files from private document folders</t>
-  </si>
-  <si>
-    <t>Supabase storage secure policy integrations</t>
-  </si>
-  <si>
-    <t>Verify that storage objects reject direct download requests without a valid signed URL.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-065</t>
-  </si>
-  <si>
-    <t>Bypassing scopes using custom headers</t>
-  </si>
-  <si>
-    <t>Server-side authorization query rules</t>
-  </si>
-  <si>
-    <t>Verify that administrative roles are checked against the database rather than request header strings.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-066</t>
-  </si>
-  <si>
-    <t>Accessing user settings through API parameters manipulation</t>
-  </si>
-  <si>
-    <t>Strict session-to-user mappings check</t>
-  </si>
-  <si>
-    <t>Verify that user preferences are linked directly to the session user ID.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-067</t>
-  </si>
-  <si>
-    <t>Viewing logs directory folders using direct requests</t>
-  </si>
-  <si>
-    <t>Web server directory index restrictions</t>
-  </si>
-  <si>
-    <t>Verify that requesting directory URLs returns a 403 instead of exposing files list.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-068</t>
-  </si>
-  <si>
-    <t>Inviting administrative users to normal family groups</t>
-  </si>
-  <si>
-    <t>Member role invitation validations</t>
-  </si>
-  <si>
-    <t>Verify that normal users cannot invite admin-level profiles to their families.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-069</t>
-  </si>
-  <si>
-    <t>Removing the owner from a family group account</t>
-  </si>
-  <si>
-    <t>Account owner status protection filters</t>
-  </si>
-  <si>
-    <t>Verify that the backend prevents deleting or removing the primary owner from a family.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-070</t>
-  </si>
-  <si>
-    <t>Modifying document ownership parameters in database</t>
-  </si>
-  <si>
-    <t>Strict document metadata write rules</t>
-  </si>
-  <si>
-    <t>Verify that update document APIs block attempts to modify the user_id foreign key field.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-071</t>
-  </si>
-  <si>
-    <t>Altering database parameters using REST endpoints queries</t>
-  </si>
-  <si>
-    <t>SQL statement query boundaries configuration</t>
-  </si>
-  <si>
-    <t>Verify that API routing logic restricts DB writes to pre-approved model schemas.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-072</t>
-  </si>
-  <si>
-    <t>Accessing configuration tables through public endpoints</t>
-  </si>
-  <si>
-    <t>Private database table permissions config</t>
-  </si>
-  <si>
-    <t>Verify that access to settings database tables is restricted to local systems.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-073</t>
-  </si>
-  <si>
-    <t>Viewing system audit logs without permission credentials</t>
-  </si>
-  <si>
-    <t>Audit trail endpoint access controls</t>
-  </si>
-  <si>
-    <t>Verify that audit APIs validate administrator permissions before exporting data logs.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-074</t>
-  </si>
-  <si>
-    <t>Triggering system backups via unauthorized requests</t>
-  </si>
-  <si>
-    <t>System administrative actions protections</t>
-  </si>
-  <si>
-    <t>Verify that database backup routes require local execution permissions.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-075</t>
-  </si>
-  <si>
-    <t>Restoring database states using modified parameters</t>
-  </si>
-  <si>
-    <t>Strict database restoration command restrictions</t>
-  </si>
-  <si>
-    <t>Verify that database restore APIs block remote requests in production.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-076</t>
-  </si>
-  <si>
-    <t>Accessing development endpoints on production servers</t>
-  </si>
-  <si>
-    <t>Development mode disabled configuration</t>
-  </si>
-  <si>
-    <t>Verify that debugging and development endpoints are disabled in production builds.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-077</t>
-  </si>
-  <si>
-    <t>Executing document parsing APIs from guest sessions</t>
-  </si>
-  <si>
-    <t>Authenticated session gatekeepers integration</t>
-  </si>
-  <si>
-    <t>Verify that document metadata parsing routes reject unauthenticated sessions.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-078</t>
-  </si>
-  <si>
-    <t>Modifying document categorization metadata lists</t>
-  </si>
-  <si>
-    <t>Admin role verification for static assets</t>
-  </si>
-  <si>
-    <t>Verify that editing master categories lists is restricted to system admin accounts.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-079</t>
-  </si>
-  <si>
-    <t>Clearing system warnings from the notification tray</t>
-  </si>
-  <si>
-    <t>Notifications ownership delete checks</t>
-  </si>
-  <si>
-    <t>Verify that deleting alerts validates notification ownership matches the active user.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-080</t>
-  </si>
-  <si>
-    <t>Reading document categories metrics globally</t>
-  </si>
-  <si>
-    <t>User group scope data boundaries check</t>
-  </si>
-  <si>
-    <t>Verify that metrics queries restrict calculations to the active user's data scope.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-081</t>
-  </si>
-  <si>
-    <t>Overwriting security control variables in database</t>
-  </si>
-  <si>
-    <t>Database column write protections config</t>
-  </si>
-  <si>
-    <t>Verify that database writes block modifications to security flag columns.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-082</t>
-  </si>
-  <si>
-    <t>Reading user profile settings by changing context parameters</t>
-  </si>
-  <si>
-    <t>Session matching lookup parameters constraint</t>
-  </si>
-  <si>
-    <t>Verify that profile detail lookups strictly map to verified token attributes.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-083</t>
-  </si>
-  <si>
-    <t>Inviting users from blocked domains to family groups</t>
-  </si>
-  <si>
-    <t>Domain whitelist validation rules</t>
-  </si>
-  <si>
-    <t>Verify that inviting family members checks that their emails belong to whitelisted domains.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-084</t>
-  </si>
-  <si>
-    <t>Deleting logs folders from the local server drive</t>
-  </si>
-  <si>
-    <t>Server file modification restriction policy</t>
-  </si>
-  <si>
-    <t>Verify that system logs directory cannot be modified or deleted via web endpoints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-085</t>
-  </si>
-  <si>
-    <t>Extracting configuration keys from environment setups</t>
-  </si>
-  <si>
-    <t>Environment configs file exposure blocks</t>
-  </si>
-  <si>
-    <t>Verify that web servers block direct requests seeking `.env` configurations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-086</t>
-  </si>
-  <si>
-    <t>Downloading document templates of other families</t>
-  </si>
-  <si>
-    <t>Template ownership access restrictions</t>
-  </si>
-  <si>
-    <t>Verify that downloading custom document templates checks family ownership privileges.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-087</t>
-  </si>
-  <si>
-    <t>Accessing search indexes of other user accounts</t>
-  </si>
-  <si>
-    <t>Search results scope boundary checks</t>
-  </si>
-  <si>
-    <t>Verify that search APIs filter results using the logged-in user's ID.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-088</t>
-  </si>
-  <si>
-    <t>Accessing document metadata logs via direct keys</t>
-  </si>
-  <si>
-    <t>Database query ownership restrictions validation</t>
-  </si>
-  <si>
-    <t>Verify that retrieving document metadata limits outputs to the active account.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-089</t>
-  </si>
-  <si>
-    <t>Adding tags to documents belonging to other users</t>
-  </si>
-  <si>
-    <t>Strict document tag ownership validation rules</t>
-  </si>
-  <si>
-    <t>Verify that appending tag items validates user ownership of the parent document.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-090</t>
-  </si>
-  <si>
-    <t>Clearing session records of other active accounts</t>
-  </si>
-  <si>
-    <t>Session record delete authorization logic</t>
-  </si>
-  <si>
-    <t>Verify that deleting active sessions validates that the session ID belongs to the user.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-091</t>
-  </si>
-  <si>
-    <t>Accessing encryption keys from memory logs</t>
-  </si>
-  <si>
-    <t>Secure memory key management parameters</t>
-  </si>
-  <si>
-    <t>Verify that cryptographic keys are stored in secure memory and never logged.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-092</t>
-  </si>
-  <si>
-    <t>Inviting users to family accounts exceeding max limits</t>
-  </si>
-  <si>
-    <t>Family member count check validation</t>
-  </si>
-  <si>
-    <t>Verify that adding new members checks that the total count does not exceed family plan limits.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-093</t>
-  </si>
-  <si>
-    <t>Accessing document metrics via REST queries parameters</t>
-  </si>
-  <si>
-    <t>Contextual authorization query constraints validation</t>
-  </si>
-  <si>
-    <t>Verify that reporting queries filter parameters using the session token user ID.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-094</t>
-  </si>
-  <si>
-    <t>Downloading bulk ZIP archives of other accounts</t>
-  </si>
-  <si>
-    <t>ZIP builder file ownership validation checks</t>
-  </si>
-  <si>
-    <t>Verify that generating bulk download archives validates ownership of all target document IDs.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-095</t>
-  </si>
-  <si>
-    <t>Accessing temporary uploads directory folder directly</t>
-  </si>
-  <si>
-    <t>Temporary storage directory access permissions</t>
-  </si>
-  <si>
-    <t>Verify that public requests are blocked from listing or downloading from the temporary folder.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-096</t>
-  </si>
-  <si>
-    <t>Triggering notifications dispatch to other users</t>
-  </si>
-  <si>
-    <t>Alert dispatcher channel validation rules</t>
-  </si>
-  <si>
-    <t>Verify that alert APIs restrict notifications target mapping to verified family members.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-097</t>
-  </si>
-  <si>
-    <t>Editing system notifications settings configuration</t>
-  </si>
-  <si>
-    <t>User alert settings database permissions</t>
-  </si>
-  <si>
-    <t>Verify that changing notification rules is restricted to the account owner.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-098</t>
-  </si>
-  <si>
-    <t>Accessing document metadata search parameters options</t>
-  </si>
-  <si>
-    <t>Strict search parameter filters validation checks</t>
-  </si>
-  <si>
-    <t>Verify that search APIs restrict results to active account categories.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-099</t>
-  </si>
-  <si>
-    <t>Deleting system warnings logs files</t>
-  </si>
-  <si>
-    <t>System logs read-only attributes setup</t>
-  </si>
-  <si>
-    <t>Verify that web APIs block delete operations seeking server system log files.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-100</t>
-  </si>
-  <si>
-    <t>Accessing database statistics using client sessions</t>
-  </si>
-  <si>
-    <t>Database query permission restriction setups</t>
-  </si>
-  <si>
-    <t>Verify that normal users cannot execute diagnostic queries on database indexes.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-101</t>
-  </si>
-  <si>
-    <t>Bypassing access controls via HTTP method overriding</t>
-  </si>
-  <si>
-    <t>Strict HTTP method whitelist configurations</t>
-  </si>
-  <si>
-    <t>Verify that routes reject requests specifying modified override headers (e.g. X-HTTP-Method-Override).</t>
-  </si>
-  <si>
-    <t>SEC-VAL-102</t>
-  </si>
-  <si>
-    <t>Accessing server cache directories on local disk</t>
-  </si>
-  <si>
-    <t>Server cache folders read-only constraints</t>
-  </si>
-  <si>
-    <t>Verify that cache data folders are locked from external read requests.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-103</t>
-  </si>
-  <si>
-    <t>Reading backend source code using web controllers</t>
-  </si>
-  <si>
-    <t>Server static file routing boundaries checks</t>
-  </si>
-  <si>
-    <t>Verify that static file routes block path directory parameters seeking source files.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-104</t>
-  </si>
-  <si>
-    <t>Altering database parameters using API URL paths</t>
-  </si>
-  <si>
-    <t>URL parameter database safety constraints</t>
-  </si>
-  <si>
-    <t>Verify that parameter queries only bind values to pre-declared fields.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-105</t>
-  </si>
-  <si>
-    <t>Submitting unauthorized scopes parameters inside JWT</t>
-  </si>
-  <si>
-    <t>Server-side scope validation validations</t>
-  </si>
-  <si>
-    <t>Verify that the server parses and checks roles directly against database status values.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-106</t>
-  </si>
-  <si>
-    <t>Bypassing access controls via headers parameters override</t>
-  </si>
-  <si>
-    <t>Strict headers authentication verification mechanisms</t>
-  </si>
-  <si>
-    <t>Verify that the server validates parameters strictly from the cryptographic token payload.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-107</t>
-  </si>
-  <si>
-    <t>Inviting users with blank names to family accounts</t>
-  </si>
-  <si>
-    <t>Invite parameter presence checks configuration</t>
-  </si>
-  <si>
-    <t>Verify that inviting family members requires entering a valid name string.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-108</t>
-  </si>
-  <si>
-    <t>Retrieving files with modified path parameters</t>
-  </si>
-  <si>
-    <t>Strict path directory structure mapping validation</t>
-  </si>
-  <si>
-    <t>Verify that resource downloads resolve inside defined storage boundaries.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-109</t>
-  </si>
-  <si>
-    <t>Modifying other active users settings profiles</t>
-  </si>
-  <si>
-    <t>Strict record matching validation rules integration</t>
-  </si>
-  <si>
-    <t>Verify that database updates validate active owner credentials before saving.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-110</t>
-  </si>
-  <si>
-    <t>Reading document attachments without security tokens</t>
-  </si>
-  <si>
-    <t>Strict attachments gateway access constraints</t>
-  </si>
-  <si>
-    <t>Verify that fetching files blocks unauthenticated requests with a 401 code.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-111</t>
-  </si>
-  <si>
-    <t>Input Validation</t>
-  </si>
-  <si>
-    <t>SQL Injection via signin email parameter</t>
-  </si>
-  <si>
-    <t>Parameterized database query constraints</t>
-  </si>
-  <si>
-    <t>Verify that email parameters inside auth routes are safely bound to prevent injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-112</t>
-  </si>
-  <si>
-    <t>SQL Injection via signin password parameter</t>
-  </si>
-  <si>
-    <t>Database parameter binding validations check</t>
-  </si>
-  <si>
-    <t>Verify that password parameters inside auth routes are bound safely to prevent injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-113</t>
-  </si>
-  <si>
-    <t>SQL Injection via documents search text queries</t>
-  </si>
-  <si>
-    <t>Strict prepared statement queries execution parameters</t>
-  </si>
-  <si>
-    <t>Verify that entering SQL commands in search parameters treats inputs as literals.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-114</t>
-  </si>
-  <si>
-    <t>SQL Injection via family member name updates input</t>
-  </si>
-  <si>
-    <t>Prepared statement query parameter bindings</t>
-  </si>
-  <si>
-    <t>Verify that family members queries bind text parameters safely to prevent injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-115</t>
-  </si>
-  <si>
-    <t>SQL Injection via registration phone inputs parameters</t>
-  </si>
-  <si>
-    <t>Database driver prepared statement configurations</t>
-  </si>
-  <si>
-    <t>Verify that phone parameters are bound as standard query values to block exploits.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-116</t>
-  </si>
-  <si>
-    <t>SQL Injection via category parameters query parameters</t>
-  </si>
-  <si>
-    <t>Strict input parameter enumerations validation checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-117</t>
-  </si>
-  <si>
-    <t>SQL Injection via tags update array parameters</t>
-  </si>
-  <si>
-    <t>Safe array input ORM query constraints</t>
-  </si>
-  <si>
-    <t>SEC-VAL-118</t>
-  </si>
-  <si>
-    <t>SQL Injection via document ID route parameters</t>
-  </si>
-  <si>
-    <t>UUID pattern route validation constraints</t>
-  </si>
-  <si>
-    <t>SEC-VAL-119</t>
-  </si>
-  <si>
-    <t>SQL Injection via notifications filter queries parameters</t>
-  </si>
-  <si>
-    <t>Database prepared statements setup verification</t>
-  </si>
-  <si>
-    <t>SEC-VAL-120</t>
-  </si>
-  <si>
-    <t>NoSQL Injection via custom JSON parameters query</t>
-  </si>
-  <si>
-    <t>JSON schema validator parameters filters check</t>
-  </si>
-  <si>
-    <t>Verify that endpoints reject objects containing NoSQL operators (e.g. $gt, $ne).</t>
-  </si>
-  <si>
-    <t>SEC-VAL-121</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document names metadata parameter</t>
-  </si>
-  <si>
-    <t>HTML entities output escaping and sanitization</t>
-  </si>
-  <si>
-    <t>SEC-VAL-122</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member details addresses attributes</t>
-  </si>
-  <si>
-    <t>Strict HTML tags inputs sanitization filters</t>
-  </si>
-  <si>
-    <t>SEC-VAL-123</t>
-  </si>
-  <si>
-    <t>Reflected XSS via categories search filter inputs</t>
-  </si>
-  <si>
-    <t>Sanitized HTTP request parameters rendering rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-124</t>
-  </si>
-  <si>
-    <t>Reflected XSS via notification ID route queries</t>
-  </si>
-  <si>
-    <t>HTML entity output encoding filters integration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-125</t>
-  </si>
-  <si>
-    <t>HTML Injection inside profile names updates parameter</t>
-  </si>
-  <si>
-    <t>HTML tags removal regex filters check</t>
-  </si>
-  <si>
-    <t>SEC-VAL-126</t>
-  </si>
-  <si>
-    <t>System command injection via upload files name attribute</t>
-  </si>
-  <si>
-    <t>Filenames random hash renaming constraints</t>
-  </si>
-  <si>
-    <t>SEC-VAL-127</t>
-  </si>
-  <si>
-    <t>Directory traversal using null byte parameters injection</t>
-  </si>
-  <si>
-    <t>Binary-safe string filter validation parameters</t>
-  </si>
-  <si>
-    <t>SEC-VAL-128</t>
-  </si>
-  <si>
-    <t>Directory traversal using boundary path strings (../)</t>
-  </si>
-  <si>
-    <t>Strict path directories boundary resolve limits</t>
-  </si>
-  <si>
-    <t>SEC-VAL-129</t>
-  </si>
-  <si>
-    <t>Buffer overflow via large text fields payloads</t>
-  </si>
-  <si>
-    <t>Schema character limit size constraints</t>
-  </si>
-  <si>
-    <t>SEC-VAL-130</t>
-  </si>
-  <si>
-    <t>Integer overflow via large file size metadata parameters</t>
-  </si>
-  <si>
-    <t>Integer boundary verification parameter checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-131</t>
-  </si>
-  <si>
-    <t>Invalid email syntax during user invitation requests</t>
-  </si>
-  <si>
-    <t>Strict email format constraint regex rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-132</t>
-  </si>
-  <si>
-    <t>Invalid mobile formatting inputs during registration</t>
-  </si>
-  <si>
-    <t>Strict digits validation filter rules configuration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-133</t>
-  </si>
-  <si>
-    <t>Application crash via malformed JSON payload bodies</t>
-  </si>
-  <si>
-    <t>Global custom JSON parsing middleware wrappers</t>
-  </si>
-  <si>
-    <t>SEC-VAL-134</t>
-  </si>
-  <si>
-    <t>Unrestricted file size memory exhaustion checks</t>
-  </si>
-  <si>
-    <t>Upload parser payload size limits configuration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-135</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document tags lists parameter</t>
-  </si>
-  <si>
-    <t>String array element sanitization filters config</t>
-  </si>
-  <si>
-    <t>SEC-VAL-136</t>
-  </si>
-  <si>
-    <t>SQL Injection via custom document sorting parameter</t>
-  </si>
-  <si>
-    <t>Sort parameters whitelist checking verification</t>
-  </si>
-  <si>
-    <t>SEC-VAL-137</t>
-  </si>
-  <si>
-    <t>SQL Injection via profile details address attributes</t>
-  </si>
-  <si>
-    <t>Database statement query parameters execution checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-138</t>
-  </si>
-  <si>
-    <t>XML External Entity injection via upload streams</t>
-  </si>
-  <si>
-    <t>External entity parsing restrictions validation rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-139</t>
-  </si>
-  <si>
-    <t>System configuration reading via environment paths traversal</t>
-  </si>
-  <si>
-    <t>Path check resolve sandbox boundary verification</t>
-  </si>
-  <si>
-    <t>SEC-VAL-140</t>
-  </si>
-  <si>
-    <t>Input parameter bypass using HTTP Parameter Pollution</t>
-  </si>
-  <si>
-    <t>Strict query parameter object parsing validators</t>
-  </si>
-  <si>
-    <t>SEC-VAL-141</t>
-  </si>
-  <si>
-    <t>Bypassing filters using URL double-encoding variables</t>
-  </si>
-  <si>
-    <t>Safe route parameter decoding filters configurations</t>
-  </si>
-  <si>
-    <t>SEC-VAL-142</t>
-  </si>
-  <si>
-    <t>Uploading batch zip files with directory traversal files</t>
-  </si>
-  <si>
-    <t>ZIP archive unpack path verification checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-143</t>
-  </si>
-  <si>
-    <t>Bypassing string checks using multi-byte Unicode strings</t>
-  </si>
-  <si>
-    <t>UTF-8 string normalization parameter checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-144</t>
-  </si>
-  <si>
-    <t>Submitting negative values to array index lookups</t>
-  </si>
-  <si>
-    <t>Index lookup unsigned boundary verification rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-145</t>
-  </si>
-  <si>
-    <t>Application crash via nested JSON object array depth</t>
-  </si>
-  <si>
-    <t>Max JSON parsing depth configuration rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-146</t>
-  </si>
-  <si>
-    <t>Uploading malicious code using document descriptions fields</t>
-  </si>
-  <si>
-    <t>Document text sanitization filter rules integrations</t>
-  </si>
-  <si>
-    <t>Verify that document descriptions strip scripting syntax elements.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-147</t>
-  </si>
-  <si>
-    <t>Bypassing date filters using invalid date formats</t>
-  </si>
-  <si>
-    <t>Strict ISO-8601 date validator validations</t>
-  </si>
-  <si>
-    <t>SEC-VAL-148</t>
-  </si>
-  <si>
-    <t>SQL Injection via document priority flag switch values</t>
-  </si>
-  <si>
-    <t>Boolean input type casting restrictions verification</t>
-  </si>
-  <si>
-    <t>SEC-VAL-149</t>
-  </si>
-  <si>
-    <t>Header Injection via custom client information parameters</t>
-  </si>
-  <si>
-    <t>HTTP response header parameters validation rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-150</t>
-  </si>
-  <si>
-    <t>Executing local server commands via path injections parameters</t>
-  </si>
-  <si>
-    <t>Safe route mapping constraints validation checks</t>
-  </si>
-  <si>
-    <t>SEC-VAL-151</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document category text fields</t>
-  </si>
-  <si>
-    <t>Strict category parameter sanitization filters config</t>
-  </si>
-  <si>
-    <t>SEC-VAL-152</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member relationship descriptions</t>
-  </si>
-  <si>
-    <t>Family member description sanitization filters config</t>
-  </si>
-  <si>
-    <t>SEC-VAL-153</t>
-  </si>
-  <si>
-    <t>Stored XSS inside notification message fields metadata</t>
-  </si>
-  <si>
-    <t>Strict alert data sanitization checks setup</t>
-  </si>
-  <si>
-    <t>Verify that custom notifications strip tags to prevent script injection.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-154</t>
-  </si>
-  <si>
-    <t>SQL Injection via family member ID route parameters</t>
-  </si>
-  <si>
-    <t>UUID structure route parameter checks configuration</t>
-  </si>
-  <si>
-    <t>Verify that family route endpoints check for valid UUID formatting.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-155</t>
-  </si>
-  <si>
-    <t>SQL Injection via user profile ID route variables</t>
-  </si>
-  <si>
-    <t>Profile route parameters format check validation</t>
-  </si>
-  <si>
-    <t>Verify that profile route parameters reject SQL command parameters.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-156</t>
-  </si>
-  <si>
-    <t>Executing command parameters in file metadata parser</t>
-  </si>
-  <si>
-    <t>File parsing parameters validation checks config</t>
-  </si>
-  <si>
-    <t>Verify that reading uploaded file fields strips out command symbols.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-157</t>
-  </si>
-  <si>
-    <t>HTML Injection via document upload source parameters</t>
-  </si>
-  <si>
-    <t>Source tag input sanitization filter parameters</t>
-  </si>
-  <si>
-    <t>SEC-VAL-158</t>
-  </si>
-  <si>
-    <t>Bypassing checks using XML schema external links</t>
-  </si>
-  <si>
-    <t>Parser disabled external references configurations</t>
-  </si>
-  <si>
-    <t>SEC-VAL-159</t>
-  </si>
-  <si>
-    <t>Bypassing database constraints using long blood groups parameters</t>
-  </si>
-  <si>
-    <t>Blood groups category input restriction validations</t>
-  </si>
-  <si>
-    <t>Verify that blood group parameters enforce strict length and string whitelist validation.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-160</t>
-  </si>
-  <si>
-    <t>Injecting script arrays inside tag parameters query</t>
-  </si>
-  <si>
-    <t>String value array validation rules checking</t>
-  </si>
-  <si>
-    <t>Verify that array values check that elements conform to string format constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-161</t>
-  </si>
-  <si>
-    <t>Bypassing string filters using multiple slash characters</t>
-  </si>
-  <si>
-    <t>Strict route normalization filters execution check</t>
-  </si>
-  <si>
-    <t>SEC-VAL-162</t>
-  </si>
-  <si>
-    <t>Accessing folder directories via relative path downloads link</t>
-  </si>
-  <si>
-    <t>Path check resolve directory boundary constraint</t>
-  </si>
-  <si>
-    <t>Verify that file downloads block parameters seeking parent drive folder directories.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-163</t>
-  </si>
-  <si>
-    <t>Executing console actions via query string parameters</t>
-  </si>
-  <si>
-    <t>Endpoint parameters type verification checking</t>
-  </si>
-  <si>
-    <t>SEC-VAL-164</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member notes details</t>
-  </si>
-  <si>
-    <t>Strict notes field sanitization check validation</t>
-  </si>
-  <si>
-    <t>SEC-VAL-165</t>
-  </si>
-  <si>
-    <t>Bypassing date structures using time parameter injections</t>
-  </si>
-  <si>
-    <t>ISO-8601 strict date structure parsing validations</t>
-  </si>
-  <si>
-    <t>SEC-VAL-166</t>
-  </si>
-  <si>
-    <t>SQL Injection via document upload category parameters</t>
-  </si>
-  <si>
-    <t>Strict category code parameters verification constraints</t>
-  </si>
-  <si>
-    <t>SEC-VAL-167</t>
-  </si>
-  <si>
-    <t>Header Injection via custom log headers inputs</t>
-  </si>
-  <si>
-    <t>Safe log formatter header sanitization integration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-168</t>
-  </si>
-  <si>
-    <t>Executing system commands in custom metadata processor</t>
-  </si>
-  <si>
-    <t>Safe processor metadata validation checking rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-169</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document descriptions details fields</t>
-  </si>
-  <si>
-    <t>Description inputs sanitization rules setup configuration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-170</t>
-  </si>
-  <si>
-    <t>Bypassing blood type checks using special characters</t>
-  </si>
-  <si>
-    <t>Strict enum-based blood type checking configuration</t>
-  </si>
-  <si>
-    <t>Verify that blood type updates reject fields that do not match the expected enum patterns.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-171</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member email address fields</t>
-  </si>
-  <si>
-    <t>Strict email input character validations configuration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-172</t>
-  </si>
-  <si>
-    <t>Bypassing numeric limitations using floating point numbers</t>
-  </si>
-  <si>
-    <t>Strict integer type parameter validation configurations</t>
-  </si>
-  <si>
-    <t>SEC-VAL-173</t>
-  </si>
-  <si>
-    <t>Stored XSS inside profile phone number fields details</t>
-  </si>
-  <si>
-    <t>Strict phone validation rules constraints integration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-174</t>
-  </si>
-  <si>
-    <t>SQL Injection via document tag deletion queries</t>
-  </si>
-  <si>
-    <t>Strict tag parameter binding configurations validation</t>
-  </si>
-  <si>
-    <t>SEC-VAL-175</t>
-  </si>
-  <si>
-    <t>Bypassing size constraints using empty parameter keys</t>
-  </si>
-  <si>
-    <t>Schema keys existence check validation rules</t>
-  </si>
-  <si>
-    <t>Verify that requests require required schema properties, blocking null parameter formats.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-176</t>
-  </si>
-  <si>
-    <t>Executing commands in user profile details parsing</t>
-  </si>
-  <si>
-    <t>Strict user profile parser validations checking rules</t>
-  </si>
-  <si>
-    <t>SEC-VAL-177</t>
-  </si>
-  <si>
-    <t>Stored XSS inside document custom category details</t>
-  </si>
-  <si>
-    <t>Strict category text inputs validations parameters</t>
-  </si>
-  <si>
-    <t>SEC-VAL-178</t>
-  </si>
-  <si>
-    <t>Bypassing type constraints using hex-encoded string parameters</t>
-  </si>
-  <si>
-    <t>Strict input decoding boundary constraints checking</t>
-  </si>
-  <si>
-    <t>Verify that hex-encoded inputs are rejected unless explicitly allowed by schema rules.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-179</t>
-  </si>
-  <si>
-    <t>Stored XSS inside family member relationship titles details</t>
-  </si>
-  <si>
-    <t>Relationship titles sanitization filter guidelines configuration</t>
-  </si>
-  <si>
-    <t>SEC-VAL-180</t>
-  </si>
-  <si>
-    <t>Bypassing size validation using array representation parameters</t>
-  </si>
-  <si>
-    <t>Strict parameter structure check validation configurations</t>
-  </si>
-  <si>
-    <t>Verify that endpoints validate parameter structure matches expected string type constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-181</t>
-  </si>
-  <si>
-    <t>Session Management</t>
-  </si>
-  <si>
-    <t>Session hijacking via predictable session credentials</t>
-  </si>
-  <si>
-    <t>Cryptographically secure session token generation keys</t>
-  </si>
-  <si>
-    <t>Verify that session identifiers are generated using secure random generators.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-182</t>
-  </si>
-  <si>
-    <t>Reading active cookies from insecure HTTP request logs</t>
-  </si>
-  <si>
-    <t>HTTPS secure connection transport policy rules</t>
-  </si>
-  <si>
-    <t>Verify that backend servers block unencrypted connections and enforce TLS configurations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-183</t>
-  </si>
-  <si>
-    <t>Accessing endpoints post active session deletion request</t>
-  </si>
-  <si>
-    <t>Database session validation verify middlewares config</t>
-  </si>
-  <si>
-    <t>Verify that deleting session records blocks immediate request authentication checks.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-184</t>
-  </si>
-  <si>
-    <t>Altering session structures using query string overrides</t>
-  </si>
-  <si>
-    <t>Strict header credentials lookup constraints configuration</t>
-  </si>
-  <si>
-    <t>Verify that access tokens parse strictly from authorization header fields.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-185</t>
-  </si>
-  <si>
-    <t>Session fixation via predefined cookie structures login</t>
-  </si>
-  <si>
-    <t>Cookie identifier regeneration on credentials success</t>
-  </si>
-  <si>
-    <t>Verify that logging in generates a completely new session identifier.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-186</t>
-  </si>
-  <si>
-    <t>Brute forcing active token payloads values check</t>
-  </si>
-  <si>
-    <t>HMAC-SHA256 signature key verification checks</t>
-  </si>
-  <si>
-    <t>Verify that signature keys enforce 256-bit cryptographical constraints.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-187</t>
-  </si>
-  <si>
-    <t>Accessing resources using cached active sessions index</t>
-  </si>
-  <si>
-    <t>Non-cacheable secure headers routing definitions</t>
-  </si>
-  <si>
-    <t>Verify that endpoints return cache control directives blocking resource storage.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-188</t>
-  </si>
-  <si>
-    <t>Reusing old token credentials after email address update</t>
-  </si>
-  <si>
-    <t>Session invalidation on profile attribute modification</t>
-  </si>
-  <si>
-    <t>Verify that updating user email invalidates current JWT access tokens.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-189</t>
-  </si>
-  <si>
-    <t>Intercepting cookies using proxy request variables modification</t>
-  </si>
-  <si>
-    <t>Secure TLS server credentials configuration verification</t>
-  </si>
-  <si>
-    <t>Verify that TLS connections check server certificate authenticity mappings.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-190</t>
-  </si>
-  <si>
-    <t>Bypassing token validations via algorithm parameters overrides</t>
-  </si>
-  <si>
-    <t>Supported algorithms whitelist checking rules configuration</t>
-  </si>
-  <si>
-    <t>Verify that signature validations reject algorithms that do not match server secret configurations.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-191</t>
-  </si>
-  <si>
-    <t>Accessing pages with expired credentials parameters check</t>
-  </si>
-  <si>
-    <t>Strict credentials lifespan validation checkers</t>
-  </si>
-  <si>
-    <t>Verify that tokens automatically invalidate upon expiration timestamps.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-192</t>
-  </si>
-  <si>
-    <t>Replaying session tokens in multi-tab active states</t>
-  </si>
-  <si>
-    <t>Single session token database lookup verification</t>
-  </si>
-  <si>
-    <t>Verify that sessions match database lookup parameters to prevent token reuse exploits.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-193</t>
-  </si>
-  <si>
-    <t>Altering token attributes inside client cookies variables</t>
-  </si>
-  <si>
-    <t>Strict cookie signature verification guidelines checks</t>
-  </si>
-  <si>
-    <t>Verify that custom cookies check cryptographical signature integrity.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-194</t>
-  </si>
-  <si>
-    <t>Accessing administrative portals using guest active cookies</t>
-  </si>
-  <si>
-    <t>Role mapping permissions check validation rules</t>
-  </si>
-  <si>
-    <t>Verify that portal routes check role permissions before authentication.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-195</t>
-  </si>
-  <si>
-    <t>Injecting characters inside session identifier query string</t>
-  </si>
-  <si>
-    <t>Strict alphanumeric session parsing rules integration</t>
-  </si>
-  <si>
-    <t>Verify that session ID strings conform strictly to alphanumeric formatting rules.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-196</t>
-  </si>
-  <si>
-    <t>Exposing session credentials in web redirection parameters</t>
-  </si>
-  <si>
-    <t>Redirection URI parameter whitelist parameters check</t>
-  </si>
-  <si>
-    <t>Verify that redirects strip token details from address parameters.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-197</t>
-  </si>
-  <si>
-    <t>Bypassing verification checks using local cache databases</t>
-  </si>
-  <si>
-    <t>Server validation on every API endpoint route</t>
-  </si>
-  <si>
-    <t>Verify that access is validated dynamically against active sessions database.</t>
-  </si>
-  <si>
-    <t>SEC-VAL-198</t>
-  </si>
-  <si>
-    <t>HMAC high-entropy key configuration parameters validations</t>
-  </si>
-  <si>
     <t>SEC-VAL-199</t>
   </si>
   <si>
@@ -3499,10 +3532,13 @@
     <t>SEC-VAL-209</t>
   </si>
   <si>
-    <t>SQL Injection via notification parameters check queries</t>
-  </si>
-  <si>
-    <t>Notification statements prepared query parameter bindings</t>
+    <t>SQL Injection via notification pagination page limits</t>
+  </si>
+  <si>
+    <t>Strict integer casting on query offsets</t>
+  </si>
+  <si>
+    <t>Verify that page and limit parameters on notification queries are converted to integers, preventing injection of SQL commands.</t>
   </si>
   <si>
     <t>SEC-VAL-210</t>
@@ -8415,7 +8451,7 @@
         <v>884</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>283</v>
+        <v>885</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>11</v>
@@ -8423,19 +8459,19 @@
     </row>
     <row r="223" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>287</v>
+        <v>889</v>
       </c>
       <c r="F223" s="7" t="s">
         <v>11</v>
@@ -8443,16 +8479,16 @@
     </row>
     <row r="224" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>291</v>
@@ -8463,16 +8499,16 @@
     </row>
     <row r="225" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E225" s="6" t="s">
         <v>295</v>
@@ -8483,19 +8519,19 @@
     </row>
     <row r="226" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>299</v>
+        <v>899</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>11</v>
@@ -8503,16 +8539,16 @@
     </row>
     <row r="227" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="E227" s="6" t="s">
         <v>303</v>
@@ -8523,16 +8559,16 @@
     </row>
     <row r="228" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>307</v>
@@ -8543,16 +8579,16 @@
     </row>
     <row r="229" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="E229" s="6" t="s">
         <v>311</v>
@@ -8563,16 +8599,16 @@
     </row>
     <row r="230" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>315</v>
@@ -8583,16 +8619,16 @@
     </row>
     <row r="231" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="E231" s="6" t="s">
         <v>319</v>
@@ -8603,16 +8639,16 @@
     </row>
     <row r="232" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>323</v>
@@ -8623,16 +8659,16 @@
     </row>
     <row r="233" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E233" s="6" t="s">
         <v>327</v>
@@ -8643,16 +8679,16 @@
     </row>
     <row r="234" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>331</v>
@@ -8663,16 +8699,16 @@
     </row>
     <row r="235" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="E235" s="6" t="s">
         <v>335</v>
@@ -8683,16 +8719,16 @@
     </row>
     <row r="236" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>339</v>
@@ -8703,16 +8739,16 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E237" s="6" t="s">
         <v>343</v>
@@ -8723,19 +8759,19 @@
     </row>
     <row r="238" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>347</v>
+        <v>936</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>11</v>
@@ -8743,16 +8779,16 @@
     </row>
     <row r="239" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="E239" s="6" t="s">
         <v>351</v>
@@ -8763,16 +8799,16 @@
     </row>
     <row r="240" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>355</v>
@@ -8783,16 +8819,16 @@
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="E241" s="6" t="s">
         <v>359</v>
@@ -8803,19 +8839,19 @@
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>11</v>
@@ -8823,16 +8859,16 @@
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E243" s="6" t="s">
         <v>367</v>
@@ -8843,19 +8879,19 @@
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>371</v>
+        <v>956</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>11</v>
@@ -8863,19 +8899,19 @@
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
-        <v>952</v>
+        <v>957</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>375</v>
+        <v>960</v>
       </c>
       <c r="F245" s="7" t="s">
         <v>11</v>
@@ -8883,19 +8919,19 @@
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>379</v>
+        <v>964</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>11</v>
@@ -8903,16 +8939,16 @@
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="E247" s="6" t="s">
         <v>383</v>
@@ -8923,16 +8959,16 @@
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>387</v>
@@ -8943,19 +8979,19 @@
     </row>
     <row r="249" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>11</v>
@@ -8963,19 +8999,19 @@
     </row>
     <row r="250" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>11</v>
@@ -8983,19 +9019,19 @@
     </row>
     <row r="251" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="B251" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="E251" s="6" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="F251" s="7" t="s">
         <v>11</v>
@@ -9003,19 +9039,19 @@
     </row>
     <row r="252" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="F252" s="4" t="s">
         <v>11</v>
@@ -9023,16 +9059,16 @@
     </row>
     <row r="253" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="B253" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="E253" s="6" t="s">
         <v>147</v>
@@ -9043,16 +9079,16 @@
     </row>
     <row r="254" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>151</v>
@@ -9063,19 +9099,19 @@
     </row>
     <row r="255" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="E255" s="6" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="F255" s="7" t="s">
         <v>11</v>
@@ -9083,19 +9119,19 @@
     </row>
     <row r="256" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>11</v>
@@ -9103,16 +9139,16 @@
     </row>
     <row r="257" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>995</v>
+        <v>1002</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="E257" s="6" t="s">
         <v>163</v>
@@ -9123,19 +9159,19 @@
     </row>
     <row r="258" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="F258" s="4" t="s">
         <v>11</v>
@@ -9143,16 +9179,16 @@
     </row>
     <row r="259" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="E259" s="6" t="s">
         <v>171</v>
@@ -9163,16 +9199,16 @@
     </row>
     <row r="260" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>175</v>
@@ -9183,16 +9219,16 @@
     </row>
     <row r="261" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="E261" s="6" t="s">
         <v>179</v>
@@ -9203,16 +9239,16 @@
     </row>
     <row r="262" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>183</v>
@@ -9223,16 +9259,16 @@
     </row>
     <row r="263" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="E263" s="6" t="s">
         <v>187</v>
@@ -9243,16 +9279,16 @@
     </row>
     <row r="264" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>191</v>
@@ -9263,16 +9299,16 @@
     </row>
     <row r="265" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="E265" s="6" t="s">
         <v>195</v>
@@ -9283,19 +9319,19 @@
     </row>
     <row r="266" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>11</v>
@@ -9303,16 +9339,16 @@
     </row>
     <row r="267" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="E267" s="6" t="s">
         <v>203</v>
@@ -9323,16 +9359,16 @@
     </row>
     <row r="268" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>207</v>
@@ -9343,19 +9379,19 @@
     </row>
     <row r="269" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>211</v>
+        <v>1042</v>
       </c>
       <c r="F269" s="7" t="s">
         <v>11</v>
@@ -9363,16 +9399,16 @@
     </row>
     <row r="270" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>215</v>
@@ -9383,19 +9419,19 @@
     </row>
     <row r="271" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="F271" s="7" t="s">
         <v>11</v>
@@ -9403,16 +9439,16 @@
     </row>
     <row r="272" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>223</v>
@@ -9423,16 +9459,16 @@
     </row>
     <row r="273" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="E273" s="6" t="s">
         <v>227</v>
@@ -9443,19 +9479,19 @@
     </row>
     <row r="274" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="F274" s="4" t="s">
         <v>11</v>
@@ -9463,19 +9499,19 @@
     </row>
     <row r="275" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>831</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>235</v>
+        <v>1063</v>
       </c>
       <c r="F275" s="7" t="s">
         <v>11</v>
@@ -9483,19 +9519,19 @@
     </row>
     <row r="276" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>831</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>1056</v>
+        <v>1065</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>11</v>
@@ -9503,19 +9539,19 @@
     </row>
     <row r="277" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>1062</v>
+        <v>1071</v>
       </c>
       <c r="E277" s="6" t="s">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="F277" s="7" t="s">
         <v>11</v>
@@ -9523,19 +9559,19 @@
     </row>
     <row r="278" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>11</v>
@@ -9543,19 +9579,19 @@
     </row>
     <row r="279" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
       <c r="E279" s="6" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="F279" s="7" t="s">
         <v>11</v>
@@ -9563,19 +9599,19 @@
     </row>
     <row r="280" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>11</v>
@@ -9583,19 +9619,19 @@
     </row>
     <row r="281" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="F281" s="7" t="s">
         <v>11</v>
@@ -9603,19 +9639,19 @@
     </row>
     <row r="282" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>11</v>
@@ -9623,19 +9659,19 @@
     </row>
     <row r="283" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="F283" s="7" t="s">
         <v>11</v>
@@ -9643,19 +9679,19 @@
     </row>
     <row r="284" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="F284" s="4" t="s">
         <v>11</v>
@@ -9663,19 +9699,19 @@
     </row>
     <row r="285" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="F285" s="7" t="s">
         <v>11</v>
@@ -9683,19 +9719,19 @@
     </row>
     <row r="286" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="F286" s="4" t="s">
         <v>11</v>
@@ -9703,19 +9739,19 @@
     </row>
     <row r="287" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="E287" s="6" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="F287" s="7" t="s">
         <v>11</v>
@@ -9723,19 +9759,19 @@
     </row>
     <row r="288" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="F288" s="4" t="s">
         <v>11</v>
@@ -9743,19 +9779,19 @@
     </row>
     <row r="289" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="E289" s="6" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="F289" s="7" t="s">
         <v>11</v>
@@ -9763,19 +9799,19 @@
     </row>
     <row r="290" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>11</v>
@@ -9783,19 +9819,19 @@
     </row>
     <row r="291" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="E291" s="6" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F291" s="7" t="s">
         <v>11</v>
@@ -9803,19 +9839,19 @@
     </row>
     <row r="292" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="F292" s="4" t="s">
         <v>11</v>
@@ -9823,19 +9859,19 @@
     </row>
     <row r="293" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="E293" s="6" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="F293" s="7" t="s">
         <v>11</v>
@@ -9843,19 +9879,19 @@
     </row>
     <row r="294" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>93</v>
+        <v>1138</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>95</v>
+        <v>1140</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>11</v>
@@ -9863,19 +9899,19 @@
     </row>
     <row r="295" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
-        <v>1130</v>
+        <v>1141</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>1131</v>
+        <v>1142</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>1132</v>
+        <v>1143</v>
       </c>
       <c r="E295" s="6" t="s">
-        <v>1133</v>
+        <v>1144</v>
       </c>
       <c r="F295" s="7" t="s">
         <v>11</v>
@@ -9883,16 +9919,16 @@
     </row>
     <row r="296" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>1135</v>
+        <v>1146</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>103</v>
@@ -9903,16 +9939,16 @@
     </row>
     <row r="297" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
-        <v>1137</v>
+        <v>1148</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>1138</v>
+        <v>1149</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>1139</v>
+        <v>1150</v>
       </c>
       <c r="E297" s="6" t="s">
         <v>107</v>
@@ -9923,16 +9959,16 @@
     </row>
     <row r="298" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>1140</v>
+        <v>1151</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>1141</v>
+        <v>1152</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>1142</v>
+        <v>1153</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>111</v>
@@ -9943,16 +9979,16 @@
     </row>
     <row r="299" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
-        <v>1143</v>
+        <v>1154</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>1144</v>
+        <v>1155</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>1145</v>
+        <v>1156</v>
       </c>
       <c r="E299" s="6" t="s">
         <v>115</v>
@@ -9963,16 +9999,16 @@
     </row>
     <row r="300" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>1146</v>
+        <v>1157</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>1147</v>
+        <v>1158</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>1148</v>
+        <v>1159</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>119</v>
@@ -9983,16 +10019,16 @@
     </row>
     <row r="301" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
-        <v>1149</v>
+        <v>1160</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1150</v>
+        <v>1161</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>1151</v>
+        <v>1162</v>
       </c>
       <c r="E301" s="6" t="s">
         <v>123</v>
@@ -10003,16 +10039,16 @@
     </row>
     <row r="302" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>1152</v>
+        <v>1163</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>1153</v>
+        <v>1164</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>1154</v>
+        <v>1165</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>127</v>
@@ -10023,16 +10059,16 @@
     </row>
     <row r="303" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
-        <v>1155</v>
+        <v>1166</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>1156</v>
+        <v>1167</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>1157</v>
+        <v>1168</v>
       </c>
       <c r="E303" s="6" t="s">
         <v>131</v>
@@ -10043,16 +10079,16 @@
     </row>
     <row r="304" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>1158</v>
+        <v>1169</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>1159</v>
+        <v>1170</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>1160</v>
+        <v>1171</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>135</v>
@@ -10063,19 +10099,19 @@
     </row>
     <row r="305" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
-        <v>1161</v>
+        <v>1172</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>1162</v>
+        <v>1173</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>1163</v>
+        <v>1174</v>
       </c>
       <c r="E305" s="6" t="s">
-        <v>139</v>
+        <v>1175</v>
       </c>
       <c r="F305" s="7" t="s">
         <v>11</v>
@@ -10083,16 +10119,16 @@
     </row>
     <row r="306" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>1164</v>
+        <v>1176</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>1166</v>
+        <v>1178</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>143</v>
